--- a/Refined_Radio_Control.xlsx
+++ b/Refined_Radio_Control.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Genres" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Song Library'!$A$2:$L$251</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Song Library'!$A$2:$L$248</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2170" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="835">
   <si>
     <t xml:space="preserve">REFINED RADIO — MASTER CONTROL SHEET</t>
   </si>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">music/Fall on U s Outlaw Country (2).mp3</t>
   </si>
   <si>
-    <t xml:space="preserve">Fall on Us (Country)</t>
+    <t xml:space="preserve">Fall on Us (Outlaw Country)</t>
   </si>
   <si>
     <t xml:space="preserve">music/FallmOn Us.mp3</t>
@@ -851,12 +851,6 @@
     <t xml:space="preserve">Grandma Said Amen Country Rap</t>
   </si>
   <si>
-    <t xml:space="preserve">Grandma Said Amen Country Rap  (Bounce Drop Remix V1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grandma Said Amen Country Rap — Remix</t>
-  </si>
-  <si>
     <t xml:space="preserve">music/Granpa was a Preacher Man (1).mp3</t>
   </si>
   <si>
@@ -1241,7 +1235,7 @@
     <t xml:space="preserve">music/(Intro _ Build-Up).mp3</t>
   </si>
   <si>
-    <t xml:space="preserve">If I Walk on Water (EDM)</t>
+    <t xml:space="preserve">I Will Walk on Water (EDM)</t>
   </si>
   <si>
     <t xml:space="preserve">If I Walk on Water</t>
@@ -1250,7 +1244,7 @@
     <t xml:space="preserve">music/In a Dry and Weary Land Country Rock.mp3</t>
   </si>
   <si>
-    <t xml:space="preserve">In a Dry and Weary Land (Country)</t>
+    <t xml:space="preserve">In a Dry and Weary Land (Psychedelic Christian Rock Version)</t>
   </si>
   <si>
     <t xml:space="preserve">In a Dry and Weary Land</t>
@@ -1361,7 +1355,7 @@
     <t xml:space="preserve">music/Lift-my-head.mp3</t>
   </si>
   <si>
-    <t xml:space="preserve">Lift My Head (1980s)</t>
+    <t xml:space="preserve">Lift My Head (80s)</t>
   </si>
   <si>
     <t xml:space="preserve">Lift My Head</t>
@@ -1469,7 +1463,7 @@
     <t xml:space="preserve">music/Midnight Grace (Studio Freestyle Worship) (1).mp3</t>
   </si>
   <si>
-    <t xml:space="preserve">Midnight Grace (Studio Freestyle Worship) (1980s)</t>
+    <t xml:space="preserve">Midnight Grace (Studio Freestyle Worship) (80s)</t>
   </si>
   <si>
     <t xml:space="preserve">Midnight Grace</t>
@@ -1523,7 +1517,7 @@
     <t xml:space="preserve">music/New Anthem Love.mp3</t>
   </si>
   <si>
-    <t xml:space="preserve">New Anthem Love (1980s)</t>
+    <t xml:space="preserve">New Anthem Love (80s)</t>
   </si>
   <si>
     <t xml:space="preserve">New Anthem Love</t>
@@ -1568,7 +1562,7 @@
     <t xml:space="preserve">music/Out of the Depths Country Rock (1).mp3</t>
   </si>
   <si>
-    <t xml:space="preserve">Out of the Depths (Country)</t>
+    <t xml:space="preserve">Out of the Depths (Psychedelic Christian Rock)</t>
   </si>
   <si>
     <t xml:space="preserve">Out of the Depths</t>
@@ -1598,21 +1592,15 @@
     <t xml:space="preserve">Overcome in Rest (Southern Blues Rock)</t>
   </si>
   <si>
-    <t xml:space="preserve">music/Pain and Rpride Radio (1).mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pain and Pride (Alternative R&amp;B)</t>
+    <t xml:space="preserve">music/Pain and Pride (1).mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pain and Pride (Blues-Jazz)</t>
   </si>
   <si>
     <t xml:space="preserve">Pain and Pride</t>
   </si>
   <si>
-    <t xml:space="preserve">music/Pain and Pride (1).mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pain and Pride (Blues-Jazz)</t>
-  </si>
-  <si>
     <t xml:space="preserve">music/Pain and Pride.mp3</t>
   </si>
   <si>
@@ -1634,7 +1622,7 @@
     <t xml:space="preserve">music/Pain and Rpride Radio.mp3</t>
   </si>
   <si>
-    <t xml:space="preserve">Pain and Pride (Alternative R&amp;B) ← (Pain and Rride fixed)</t>
+    <t xml:space="preserve">Pain and Pride (Alternative R&amp;B) </t>
   </si>
   <si>
     <t xml:space="preserve">Pain and Rride</t>
@@ -1805,12 +1793,6 @@
     <t xml:space="preserve">Sippin’ on Grace &amp; Truth Country Rap</t>
   </si>
   <si>
-    <t xml:space="preserve">Sippin’ on Grace &amp; Truth (Country Rap Bounce Drop) — Remix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sippin’ on Grace &amp; Truth Country Rap — Remix</t>
-  </si>
-  <si>
     <t xml:space="preserve">music/Spoken For (1).mp3</t>
   </si>
   <si>
@@ -1850,7 +1832,7 @@
     <t xml:space="preserve">music/Stay in Your Love” (Smooth Groove Version)_.mp3</t>
   </si>
   <si>
-    <t xml:space="preserve">Stay in Your Love (Smooth Groove Version) (1980s)</t>
+    <t xml:space="preserve">Stay in Your Love (Smooth Groove Version) (80s)</t>
   </si>
   <si>
     <t xml:space="preserve">Stay in Your Love</t>
@@ -2063,7 +2045,7 @@
     <t xml:space="preserve">music/The Nitty Gritty Devil Country Rock (1).mp3</t>
   </si>
   <si>
-    <t xml:space="preserve">The Nitty Gritty Devil (Country)</t>
+    <t xml:space="preserve">The Nitty Gritty Devil (Psychedelic Christian Rock)</t>
   </si>
   <si>
     <t xml:space="preserve">The Nitty Gritty Devil</t>
@@ -2138,7 +2120,7 @@
     <t xml:space="preserve">Tongues of Fire Country Rap</t>
   </si>
   <si>
-    <t xml:space="preserve">Tongues of Fire Country Rap — Remix (Bounce Drop)</t>
+    <t xml:space="preserve">Tongues of Fire Country Rap — Remix (Alternative 2000s Rock)</t>
   </si>
   <si>
     <t xml:space="preserve">Tongues of Fire Country Rap — Remix</t>
@@ -2393,6 +2375,48 @@
     <t xml:space="preserve">Your Holy Heartbeat Stays (Concert Mix) (Stage Style)</t>
   </si>
   <si>
+    <t xml:space="preserve">music/The Way You Lead Me  (Alt 2000s Rock).mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Way You Lead Me (Alt Rock)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alt Rock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Way You Lead Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">music/He Never Quit on Me (Alternative 2000s Rock).mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He Never Quit on Me (Alt Rock)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He Never Quit on Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">music/He Spoke to the Wind (80s).mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He Spoke to the Wind (80s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He Spoke to the Wind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">music/Awoken the Master (Southern Blues Rock).mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awoken the Master (Southern Blues Rock)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awoken the Master</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rule</t>
   </si>
   <si>
@@ -2481,9 +2505,6 @@
   </si>
   <si>
     <t xml:space="preserve">christian pop; southern christian rock; christian country; christian country - pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80s</t>
   </si>
   <si>
     <t xml:space="preserve">Workday Encouragement</t>
@@ -2670,7 +2691,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2703,7 +2724,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2711,7 +2736,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3106,7 +3135,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L251"/>
+  <dimension ref="A1:L252"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3203,7 +3232,7 @@
         <v>31</v>
       </c>
       <c r="I3" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H3)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H3)</f>
         <v>1</v>
       </c>
       <c r="J3" s="6"/>
@@ -3238,7 +3267,7 @@
         <v>37</v>
       </c>
       <c r="I4" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H4)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H4)</f>
         <v>1</v>
       </c>
       <c r="J4" s="6"/>
@@ -3273,7 +3302,7 @@
         <v>42</v>
       </c>
       <c r="I5" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H5)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H5)</f>
         <v>2</v>
       </c>
       <c r="J5" s="6"/>
@@ -3308,7 +3337,7 @@
         <v>42</v>
       </c>
       <c r="I6" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H6)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H6)</f>
         <v>2</v>
       </c>
       <c r="J6" s="6"/>
@@ -3343,7 +3372,7 @@
         <v>51</v>
       </c>
       <c r="I7" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H7)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H7)</f>
         <v>1</v>
       </c>
       <c r="J7" s="6"/>
@@ -3378,7 +3407,7 @@
         <v>56</v>
       </c>
       <c r="I8" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H8)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H8)</f>
         <v>1</v>
       </c>
       <c r="J8" s="7" t="s">
@@ -3415,7 +3444,7 @@
         <v>60</v>
       </c>
       <c r="I9" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H9)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H9)</f>
         <v>1</v>
       </c>
       <c r="J9" s="7" t="s">
@@ -3452,7 +3481,7 @@
         <v>63</v>
       </c>
       <c r="I10" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H10)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H10)</f>
         <v>1</v>
       </c>
       <c r="J10" s="6"/>
@@ -3487,7 +3516,7 @@
         <v>66</v>
       </c>
       <c r="I11" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H11)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H11)</f>
         <v>1</v>
       </c>
       <c r="J11" s="6"/>
@@ -3522,7 +3551,7 @@
         <v>71</v>
       </c>
       <c r="I12" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H12)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H12)</f>
         <v>1</v>
       </c>
       <c r="J12" s="6"/>
@@ -3557,7 +3586,7 @@
         <v>74</v>
       </c>
       <c r="I13" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H13)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H13)</f>
         <v>1</v>
       </c>
       <c r="J13" s="6"/>
@@ -3592,7 +3621,7 @@
         <v>79</v>
       </c>
       <c r="I14" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H14)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H14)</f>
         <v>1</v>
       </c>
       <c r="J14" s="6"/>
@@ -3627,7 +3656,7 @@
         <v>84</v>
       </c>
       <c r="I15" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H15)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H15)</f>
         <v>1</v>
       </c>
       <c r="J15" s="7" t="s">
@@ -3638,7 +3667,7 @@
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="n">
         <v>17</v>
       </c>
@@ -3664,7 +3693,7 @@
         <v>89</v>
       </c>
       <c r="I16" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H16)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H16)</f>
         <v>1</v>
       </c>
       <c r="J16" s="6"/>
@@ -3699,7 +3728,7 @@
         <v>94</v>
       </c>
       <c r="I17" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H17)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H17)</f>
         <v>1</v>
       </c>
       <c r="J17" s="7" t="s">
@@ -3736,7 +3765,7 @@
         <v>98</v>
       </c>
       <c r="I18" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H18)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H18)</f>
         <v>1</v>
       </c>
       <c r="J18" s="6"/>
@@ -3771,7 +3800,7 @@
         <v>103</v>
       </c>
       <c r="I19" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H19)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H19)</f>
         <v>1</v>
       </c>
       <c r="J19" s="6"/>
@@ -3806,7 +3835,7 @@
         <v>106</v>
       </c>
       <c r="I20" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H20)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H20)</f>
         <v>1</v>
       </c>
       <c r="J20" s="6"/>
@@ -3841,7 +3870,7 @@
         <v>111</v>
       </c>
       <c r="I21" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H21)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H21)</f>
         <v>1</v>
       </c>
       <c r="J21" s="7" t="s">
@@ -3878,7 +3907,7 @@
         <v>115</v>
       </c>
       <c r="I22" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H22)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H22)</f>
         <v>1</v>
       </c>
       <c r="J22" s="6"/>
@@ -3913,7 +3942,7 @@
         <v>118</v>
       </c>
       <c r="I23" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H23)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H23)</f>
         <v>1</v>
       </c>
       <c r="J23" s="6"/>
@@ -3948,7 +3977,7 @@
         <v>123</v>
       </c>
       <c r="I24" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H24)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H24)</f>
         <v>1</v>
       </c>
       <c r="J24" s="6"/>
@@ -3983,7 +4012,7 @@
         <v>126</v>
       </c>
       <c r="I25" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H25)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H25)</f>
         <v>1</v>
       </c>
       <c r="J25" s="6"/>
@@ -4018,7 +4047,7 @@
         <v>129</v>
       </c>
       <c r="I26" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H26)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H26)</f>
         <v>1</v>
       </c>
       <c r="J26" s="6"/>
@@ -4053,7 +4082,7 @@
         <v>132</v>
       </c>
       <c r="I27" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H27)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H27)</f>
         <v>1</v>
       </c>
       <c r="J27" s="6"/>
@@ -4088,7 +4117,7 @@
         <v>135</v>
       </c>
       <c r="I28" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H28)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H28)</f>
         <v>1</v>
       </c>
       <c r="J28" s="6"/>
@@ -4123,7 +4152,7 @@
         <v>138</v>
       </c>
       <c r="I29" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H29)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H29)</f>
         <v>1</v>
       </c>
       <c r="J29" s="6"/>
@@ -4158,7 +4187,7 @@
         <v>143</v>
       </c>
       <c r="I30" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H30)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H30)</f>
         <v>1</v>
       </c>
       <c r="J30" s="7" t="s">
@@ -4195,7 +4224,7 @@
         <v>146</v>
       </c>
       <c r="I31" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H31)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H31)</f>
         <v>2</v>
       </c>
       <c r="J31" s="6"/>
@@ -4230,7 +4259,7 @@
         <v>146</v>
       </c>
       <c r="I32" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H32)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H32)</f>
         <v>2</v>
       </c>
       <c r="J32" s="6"/>
@@ -4265,7 +4294,7 @@
         <v>151</v>
       </c>
       <c r="I33" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H33)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H33)</f>
         <v>1</v>
       </c>
       <c r="J33" s="6"/>
@@ -4300,7 +4329,7 @@
         <v>154</v>
       </c>
       <c r="I34" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H34)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H34)</f>
         <v>2</v>
       </c>
       <c r="J34" s="6"/>
@@ -4335,7 +4364,7 @@
         <v>154</v>
       </c>
       <c r="I35" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H35)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H35)</f>
         <v>2</v>
       </c>
       <c r="J35" s="6"/>
@@ -4370,7 +4399,7 @@
         <v>161</v>
       </c>
       <c r="I36" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H36)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H36)</f>
         <v>1</v>
       </c>
       <c r="J36" s="6"/>
@@ -4405,7 +4434,7 @@
         <v>164</v>
       </c>
       <c r="I37" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H37)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H37)</f>
         <v>1</v>
       </c>
       <c r="J37" s="6"/>
@@ -4440,7 +4469,7 @@
         <v>167</v>
       </c>
       <c r="I38" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H38)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H38)</f>
         <v>2</v>
       </c>
       <c r="J38" s="6"/>
@@ -4475,7 +4504,7 @@
         <v>167</v>
       </c>
       <c r="I39" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H39)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H39)</f>
         <v>2</v>
       </c>
       <c r="J39" s="6"/>
@@ -4510,7 +4539,7 @@
         <v>172</v>
       </c>
       <c r="I40" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H40)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H40)</f>
         <v>1</v>
       </c>
       <c r="J40" s="6"/>
@@ -4545,7 +4574,7 @@
         <v>177</v>
       </c>
       <c r="I41" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H41)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H41)</f>
         <v>1</v>
       </c>
       <c r="J41" s="6"/>
@@ -4580,7 +4609,7 @@
         <v>180</v>
       </c>
       <c r="I42" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H42)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H42)</f>
         <v>1</v>
       </c>
       <c r="J42" s="6"/>
@@ -4615,7 +4644,7 @@
         <v>183</v>
       </c>
       <c r="I43" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H43)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H43)</f>
         <v>1</v>
       </c>
       <c r="J43" s="7" t="s">
@@ -4652,7 +4681,7 @@
         <v>186</v>
       </c>
       <c r="I44" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H44)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H44)</f>
         <v>1</v>
       </c>
       <c r="J44" s="7" t="s">
@@ -4689,7 +4718,7 @@
         <v>189</v>
       </c>
       <c r="I45" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H45)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H45)</f>
         <v>1</v>
       </c>
       <c r="J45" s="6"/>
@@ -4724,7 +4753,7 @@
         <v>194</v>
       </c>
       <c r="I46" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H46)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H46)</f>
         <v>1</v>
       </c>
       <c r="J46" s="6"/>
@@ -4759,7 +4788,7 @@
         <v>197</v>
       </c>
       <c r="I47" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H47)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H47)</f>
         <v>2</v>
       </c>
       <c r="J47" s="6"/>
@@ -4794,7 +4823,7 @@
         <v>197</v>
       </c>
       <c r="I48" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H48)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H48)</f>
         <v>2</v>
       </c>
       <c r="J48" s="6"/>
@@ -4829,7 +4858,7 @@
         <v>204</v>
       </c>
       <c r="I49" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H49)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H49)</f>
         <v>3</v>
       </c>
       <c r="J49" s="6"/>
@@ -4855,16 +4884,16 @@
         <v>28</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>204</v>
       </c>
       <c r="I50" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H50)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H50)</f>
         <v>3</v>
       </c>
       <c r="J50" s="6"/>
@@ -4899,7 +4928,7 @@
         <v>204</v>
       </c>
       <c r="I51" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H51)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H51)</f>
         <v>3</v>
       </c>
       <c r="J51" s="6"/>
@@ -4934,7 +4963,7 @@
         <v>211</v>
       </c>
       <c r="I52" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H52)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H52)</f>
         <v>1</v>
       </c>
       <c r="J52" s="6"/>
@@ -4969,7 +4998,7 @@
         <v>214</v>
       </c>
       <c r="I53" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H53)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H53)</f>
         <v>1</v>
       </c>
       <c r="J53" s="6"/>
@@ -5004,7 +5033,7 @@
         <v>217</v>
       </c>
       <c r="I54" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H54)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H54)</f>
         <v>1</v>
       </c>
       <c r="J54" s="6"/>
@@ -5039,7 +5068,7 @@
         <v>220</v>
       </c>
       <c r="I55" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H55)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H55)</f>
         <v>2</v>
       </c>
       <c r="J55" s="6"/>
@@ -5074,7 +5103,7 @@
         <v>220</v>
       </c>
       <c r="I56" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H56)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H56)</f>
         <v>2</v>
       </c>
       <c r="J56" s="6"/>
@@ -5109,7 +5138,7 @@
         <v>225</v>
       </c>
       <c r="I57" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H57)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H57)</f>
         <v>2</v>
       </c>
       <c r="J57" s="6"/>
@@ -5144,7 +5173,7 @@
         <v>225</v>
       </c>
       <c r="I58" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H58)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H58)</f>
         <v>2</v>
       </c>
       <c r="J58" s="6"/>
@@ -5179,7 +5208,7 @@
         <v>231</v>
       </c>
       <c r="I59" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H59)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H59)</f>
         <v>1</v>
       </c>
       <c r="J59" s="6"/>
@@ -5214,7 +5243,7 @@
         <v>236</v>
       </c>
       <c r="I60" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H60)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H60)</f>
         <v>1</v>
       </c>
       <c r="J60" s="6"/>
@@ -5249,7 +5278,7 @@
         <v>239</v>
       </c>
       <c r="I61" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H61)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H61)</f>
         <v>2</v>
       </c>
       <c r="J61" s="6"/>
@@ -5284,7 +5313,7 @@
         <v>239</v>
       </c>
       <c r="I62" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H62)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H62)</f>
         <v>2</v>
       </c>
       <c r="J62" s="6"/>
@@ -5319,7 +5348,7 @@
         <v>244</v>
       </c>
       <c r="I63" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H63)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H63)</f>
         <v>1</v>
       </c>
       <c r="J63" s="6" t="s">
@@ -5356,7 +5385,7 @@
         <v>249</v>
       </c>
       <c r="I64" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H64)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H64)</f>
         <v>1</v>
       </c>
       <c r="J64" s="6"/>
@@ -5391,7 +5420,7 @@
         <v>252</v>
       </c>
       <c r="I65" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H65)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H65)</f>
         <v>1</v>
       </c>
       <c r="J65" s="6"/>
@@ -5426,7 +5455,7 @@
         <v>255</v>
       </c>
       <c r="I66" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H66)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H66)</f>
         <v>1</v>
       </c>
       <c r="J66" s="6"/>
@@ -5461,7 +5490,7 @@
         <v>258</v>
       </c>
       <c r="I67" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H67)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H67)</f>
         <v>1</v>
       </c>
       <c r="J67" s="6"/>
@@ -5496,7 +5525,7 @@
         <v>261</v>
       </c>
       <c r="I68" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H68)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H68)</f>
         <v>1</v>
       </c>
       <c r="J68" s="6" t="s">
@@ -5533,7 +5562,7 @@
         <v>264</v>
       </c>
       <c r="I69" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H69)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H69)</f>
         <v>1</v>
       </c>
       <c r="J69" s="6"/>
@@ -5568,7 +5597,7 @@
         <v>267</v>
       </c>
       <c r="I70" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H70)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H70)</f>
         <v>1</v>
       </c>
       <c r="J70" s="6"/>
@@ -5603,7 +5632,7 @@
         <v>270</v>
       </c>
       <c r="I71" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H71)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H71)</f>
         <v>1</v>
       </c>
       <c r="J71" s="6"/>
@@ -5638,7 +5667,7 @@
         <v>273</v>
       </c>
       <c r="I72" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H72)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H72)</f>
         <v>1</v>
       </c>
       <c r="J72" s="6"/>
@@ -5649,31 +5678,31 @@
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="G73" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B73" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G73" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="H73" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I73" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H73)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H73)</f>
         <v>1</v>
       </c>
       <c r="J73" s="6"/>
@@ -5684,32 +5713,32 @@
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I74" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H74)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H74)</f>
+        <v>2</v>
       </c>
       <c r="J74" s="6"/>
       <c r="K74" s="6" t="s">
@@ -5719,31 +5748,31 @@
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C75" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="D75" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G75" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>281</v>
-      </c>
       <c r="I75" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H75)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H75)</f>
         <v>2</v>
       </c>
       <c r="J75" s="6"/>
@@ -5754,32 +5783,32 @@
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="I76" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H76)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H76)</f>
+        <v>1</v>
       </c>
       <c r="J76" s="6"/>
       <c r="K76" s="6" t="s">
@@ -5789,31 +5818,31 @@
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>287</v>
+        <v>45</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>288</v>
+        <v>45</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I77" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H77)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H77)</f>
         <v>1</v>
       </c>
       <c r="J77" s="6"/>
@@ -5824,31 +5853,31 @@
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I78" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H78)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H78)</f>
         <v>1</v>
       </c>
       <c r="J78" s="6"/>
@@ -5859,31 +5888,31 @@
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I79" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H79)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H79)</f>
         <v>1</v>
       </c>
       <c r="J79" s="6"/>
@@ -5894,31 +5923,31 @@
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I80" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H80)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H80)</f>
         <v>1</v>
       </c>
       <c r="J80" s="6"/>
@@ -5929,31 +5958,31 @@
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I81" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H81)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H81)</f>
         <v>1</v>
       </c>
       <c r="J81" s="6"/>
@@ -5964,16 +5993,16 @@
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>28</v>
@@ -5985,11 +6014,11 @@
         <v>122</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I82" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H82)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H82)</f>
+        <v>3</v>
       </c>
       <c r="J82" s="6"/>
       <c r="K82" s="6" t="s">
@@ -5999,31 +6028,31 @@
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C83" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H83" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="D83" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F83" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>307</v>
-      </c>
       <c r="I83" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H83)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H83)</f>
         <v>3</v>
       </c>
       <c r="J83" s="6"/>
@@ -6034,7 +6063,7 @@
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>25</v>
@@ -6043,22 +6072,22 @@
         <v>308</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>284</v>
+        <v>69</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>284</v>
+        <v>70</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="I84" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H84)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H84)</f>
         <v>3</v>
       </c>
       <c r="J84" s="6"/>
@@ -6069,32 +6098,32 @@
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C85" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D85" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="D85" s="6" t="s">
-        <v>306</v>
-      </c>
       <c r="E85" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I85" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H85)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H85)</f>
+        <v>2</v>
       </c>
       <c r="J85" s="6"/>
       <c r="K85" s="6" t="s">
@@ -6104,31 +6133,31 @@
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C86" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H86" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D86" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G86" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>313</v>
-      </c>
       <c r="I86" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H86)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H86)</f>
         <v>2</v>
       </c>
       <c r="J86" s="6"/>
@@ -6139,7 +6168,7 @@
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>25</v>
@@ -6154,17 +6183,17 @@
         <v>28</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>230</v>
+        <v>35</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I87" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H87)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H87)</f>
+        <v>1</v>
       </c>
       <c r="J87" s="6"/>
       <c r="K87" s="6" t="s">
@@ -6174,31 +6203,31 @@
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>36</v>
+        <v>230</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I88" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H88)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H88)</f>
         <v>1</v>
       </c>
       <c r="J88" s="6"/>
@@ -6209,31 +6238,31 @@
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>230</v>
+        <v>121</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>230</v>
+        <v>122</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I89" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H89)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H89)</f>
         <v>1</v>
       </c>
       <c r="J89" s="6"/>
@@ -6244,34 +6273,36 @@
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>122</v>
+        <v>41</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I90" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H90)</f>
-        <v>1</v>
-      </c>
-      <c r="J90" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H90)</f>
+        <v>1</v>
+      </c>
+      <c r="J90" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K90" s="6" t="s">
         <v>32</v>
       </c>
@@ -6279,36 +6310,34 @@
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I91" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H91)</f>
-        <v>1</v>
-      </c>
-      <c r="J91" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H91)</f>
+        <v>2</v>
+      </c>
+      <c r="J91" s="6"/>
       <c r="K91" s="6" t="s">
         <v>32</v>
       </c>
@@ -6316,31 +6345,31 @@
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C92" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H92" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="D92" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G92" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>330</v>
-      </c>
       <c r="I92" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H92)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H92)</f>
         <v>2</v>
       </c>
       <c r="J92" s="6"/>
@@ -6351,7 +6380,7 @@
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>25</v>
@@ -6366,19 +6395,21 @@
         <v>28</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>230</v>
+        <v>40</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>230</v>
+        <v>41</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="I93" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H93)</f>
-        <v>2</v>
-      </c>
-      <c r="J93" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H93)</f>
+        <v>1</v>
+      </c>
+      <c r="J93" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K93" s="6" t="s">
         <v>32</v>
       </c>
@@ -6386,36 +6417,34 @@
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I94" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H94)</f>
-        <v>1</v>
-      </c>
-      <c r="J94" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H94)</f>
+        <v>1</v>
+      </c>
+      <c r="J94" s="6"/>
       <c r="K94" s="6" t="s">
         <v>32</v>
       </c>
@@ -6423,16 +6452,16 @@
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>28</v>
@@ -6444,10 +6473,10 @@
         <v>122</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I95" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H95)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H95)</f>
         <v>1</v>
       </c>
       <c r="J95" s="6"/>
@@ -6458,16 +6487,16 @@
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>28</v>
@@ -6479,10 +6508,10 @@
         <v>122</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I96" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H96)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H96)</f>
         <v>1</v>
       </c>
       <c r="J96" s="6"/>
@@ -6493,31 +6522,31 @@
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I97" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H97)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H97)</f>
         <v>1</v>
       </c>
       <c r="J97" s="6"/>
@@ -6528,34 +6557,36 @@
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>141</v>
+        <v>348</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>142</v>
+        <v>349</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="I98" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H98)</f>
-        <v>1</v>
-      </c>
-      <c r="J98" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H98)</f>
+        <v>1</v>
+      </c>
+      <c r="J98" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K98" s="6" t="s">
         <v>32</v>
       </c>
@@ -6563,31 +6594,31 @@
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E99" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>350</v>
+        <v>141</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>351</v>
+        <v>142</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I99" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H99)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H99)</f>
         <v>1</v>
       </c>
       <c r="J99" s="7" t="s">
@@ -6600,36 +6631,34 @@
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>141</v>
+        <v>234</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>142</v>
+        <v>235</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I100" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H100)</f>
-        <v>1</v>
-      </c>
-      <c r="J100" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H100)</f>
+        <v>3</v>
+      </c>
+      <c r="J100" s="6"/>
       <c r="K100" s="6" t="s">
         <v>32</v>
       </c>
@@ -6637,31 +6666,31 @@
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C101" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H101" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="D101" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="H101" s="4" t="s">
-        <v>358</v>
-      </c>
       <c r="I101" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H101)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H101)</f>
         <v>3</v>
       </c>
       <c r="J101" s="6"/>
@@ -6672,7 +6701,7 @@
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>25</v>
@@ -6687,16 +6716,16 @@
         <v>28</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>193</v>
+        <v>235</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I102" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H102)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H102)</f>
         <v>3</v>
       </c>
       <c r="J102" s="6"/>
@@ -6705,9 +6734,9 @@
       </c>
       <c r="L102" s="4"/>
     </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>25</v>
@@ -6722,17 +6751,17 @@
         <v>28</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>234</v>
+        <v>69</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="I103" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H103)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H103)</f>
+        <v>1</v>
       </c>
       <c r="J103" s="6"/>
       <c r="K103" s="6" t="s">
@@ -6742,31 +6771,31 @@
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="4" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I104" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H104)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H104)</f>
         <v>1</v>
       </c>
       <c r="J104" s="6"/>
@@ -6777,34 +6806,36 @@
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="4" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E105" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I105" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H105)</f>
-        <v>1</v>
-      </c>
-      <c r="J105" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H105)</f>
+        <v>1</v>
+      </c>
+      <c r="J105" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K105" s="6" t="s">
         <v>32</v>
       </c>
@@ -6812,31 +6843,31 @@
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="4" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>54</v>
+        <v>372</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>55</v>
+        <v>373</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="I106" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H106)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H106)</f>
         <v>1</v>
       </c>
       <c r="J106" s="7" t="s">
@@ -6849,36 +6880,34 @@
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="4" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E107" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>374</v>
+        <v>141</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>375</v>
+        <v>142</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="I107" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H107)</f>
-        <v>1</v>
-      </c>
-      <c r="J107" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H107)</f>
+        <v>1</v>
+      </c>
+      <c r="J107" s="6"/>
       <c r="K107" s="6" t="s">
         <v>32</v>
       </c>
@@ -6886,31 +6915,31 @@
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>141</v>
+        <v>202</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I108" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H108)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H108)</f>
         <v>1</v>
       </c>
       <c r="J108" s="6"/>
@@ -6921,34 +6950,36 @@
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E109" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>202</v>
+        <v>92</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>203</v>
+        <v>93</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I109" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H109)</f>
-        <v>1</v>
-      </c>
-      <c r="J109" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H109)</f>
+        <v>1</v>
+      </c>
+      <c r="J109" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K109" s="6" t="s">
         <v>32</v>
       </c>
@@ -6956,36 +6987,34 @@
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I110" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H110)</f>
-        <v>1</v>
-      </c>
-      <c r="J110" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H110)</f>
+        <v>1</v>
+      </c>
+      <c r="J110" s="6"/>
       <c r="K110" s="6" t="s">
         <v>32</v>
       </c>
@@ -6993,31 +7022,31 @@
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>87</v>
+        <v>202</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>88</v>
+        <v>203</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I111" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H111)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H111)</f>
         <v>1</v>
       </c>
       <c r="J111" s="6"/>
@@ -7028,31 +7057,31 @@
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>202</v>
+        <v>121</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>203</v>
+        <v>122</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I112" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H112)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H112)</f>
         <v>1</v>
       </c>
       <c r="J112" s="6"/>
@@ -7063,31 +7092,31 @@
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>121</v>
+        <v>395</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>122</v>
+        <v>396</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="I113" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H113)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H113)</f>
         <v>1</v>
       </c>
       <c r="J113" s="6"/>
@@ -7098,34 +7127,36 @@
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="4" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>397</v>
+        <v>54</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>398</v>
+        <v>55</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I114" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H114)</f>
-        <v>1</v>
-      </c>
-      <c r="J114" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H114)</f>
+        <v>1</v>
+      </c>
+      <c r="J114" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K114" s="6" t="s">
         <v>32</v>
       </c>
@@ -7133,36 +7164,34 @@
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="4" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E115" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>55</v>
+        <v>122</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I115" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H115)</f>
-        <v>1</v>
-      </c>
-      <c r="J115" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H115)</f>
+        <v>1</v>
+      </c>
+      <c r="J115" s="6"/>
       <c r="K115" s="6" t="s">
         <v>32</v>
       </c>
@@ -7170,32 +7199,32 @@
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="4" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I116" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H116)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H116)</f>
+        <v>2</v>
       </c>
       <c r="J116" s="6"/>
       <c r="K116" s="6" t="s">
@@ -7205,31 +7234,31 @@
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="4" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C117" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H117" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="D117" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="E117" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="G117" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>408</v>
-      </c>
       <c r="I117" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H117)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H117)</f>
         <v>2</v>
       </c>
       <c r="J117" s="6"/>
@@ -7240,7 +7269,7 @@
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="4" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>25</v>
@@ -7261,11 +7290,11 @@
         <v>102</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="I118" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H118)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H118)</f>
+        <v>1</v>
       </c>
       <c r="J118" s="6"/>
       <c r="K118" s="6" t="s">
@@ -7275,34 +7304,36 @@
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="4" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E119" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>101</v>
+        <v>348</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>102</v>
+        <v>349</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I119" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H119)</f>
-        <v>1</v>
-      </c>
-      <c r="J119" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H119)</f>
+        <v>1</v>
+      </c>
+      <c r="J119" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K119" s="6" t="s">
         <v>32</v>
       </c>
@@ -7310,31 +7341,31 @@
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="4" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>351</v>
+        <v>83</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I120" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H120)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H120)</f>
         <v>1</v>
       </c>
       <c r="J120" s="7" t="s">
@@ -7347,36 +7378,34 @@
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="4" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I121" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H121)</f>
-        <v>1</v>
-      </c>
-      <c r="J121" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H121)</f>
+        <v>1</v>
+      </c>
+      <c r="J121" s="6"/>
       <c r="K121" s="6" t="s">
         <v>32</v>
       </c>
@@ -7384,31 +7413,31 @@
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="4" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>49</v>
+        <v>395</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>50</v>
+        <v>396</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I122" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H122)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H122)</f>
         <v>1</v>
       </c>
       <c r="J122" s="6"/>
@@ -7419,32 +7448,32 @@
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="4" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E123" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>397</v>
+        <v>121</v>
       </c>
       <c r="G123" s="6" t="s">
-        <v>398</v>
+        <v>122</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I123" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H123)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H123)</f>
+        <v>2</v>
       </c>
       <c r="J123" s="6"/>
       <c r="K123" s="6" t="s">
@@ -7454,16 +7483,16 @@
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="4" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>28</v>
@@ -7475,10 +7504,10 @@
         <v>122</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I124" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H124)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H124)</f>
         <v>2</v>
       </c>
       <c r="J124" s="6"/>
@@ -7489,7 +7518,7 @@
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="4" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>25</v>
@@ -7504,17 +7533,17 @@
         <v>28</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="G125" s="6" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="I125" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H125)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H125)</f>
+        <v>1</v>
       </c>
       <c r="J125" s="6"/>
       <c r="K125" s="6" t="s">
@@ -7524,31 +7553,31 @@
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="4" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I126" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H126)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H126)</f>
         <v>1</v>
       </c>
       <c r="J126" s="6"/>
@@ -7559,31 +7588,31 @@
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="4" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>159</v>
+        <v>49</v>
       </c>
       <c r="G127" s="6" t="s">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="I127" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H127)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H127)</f>
         <v>1</v>
       </c>
       <c r="J127" s="6"/>
@@ -7594,34 +7623,36 @@
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="4" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>49</v>
+        <v>372</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>50</v>
+        <v>373</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I128" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H128)</f>
-        <v>1</v>
-      </c>
-      <c r="J128" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H128)</f>
+        <v>1</v>
+      </c>
+      <c r="J128" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K128" s="6" t="s">
         <v>32</v>
       </c>
@@ -7629,36 +7660,34 @@
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E129" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>374</v>
+        <v>234</v>
       </c>
       <c r="G129" s="6" t="s">
-        <v>375</v>
+        <v>235</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I129" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H129)</f>
-        <v>1</v>
-      </c>
-      <c r="J129" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H129)</f>
+        <v>3</v>
+      </c>
+      <c r="J129" s="6"/>
       <c r="K129" s="6" t="s">
         <v>32</v>
       </c>
@@ -7666,31 +7695,31 @@
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="4" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C130" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G130" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H130" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="D130" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="E130" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F130" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="G130" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="H130" s="4" t="s">
-        <v>445</v>
-      </c>
       <c r="I130" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H130)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H130)</f>
         <v>3</v>
       </c>
       <c r="J130" s="6"/>
@@ -7701,7 +7730,7 @@
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="4" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>25</v>
@@ -7716,16 +7745,16 @@
         <v>28</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="H131" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I131" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H131)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H131)</f>
         <v>3</v>
       </c>
       <c r="J131" s="6"/>
@@ -7736,7 +7765,7 @@
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="4" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>25</v>
@@ -7751,17 +7780,17 @@
         <v>28</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>141</v>
+        <v>282</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>142</v>
+        <v>282</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="I132" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H132)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H132)</f>
+        <v>1</v>
       </c>
       <c r="J132" s="6"/>
       <c r="K132" s="6" t="s">
@@ -7771,34 +7800,36 @@
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="4" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E133" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>284</v>
+        <v>92</v>
       </c>
       <c r="G133" s="6" t="s">
-        <v>284</v>
+        <v>93</v>
       </c>
       <c r="H133" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I133" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H133)</f>
-        <v>1</v>
-      </c>
-      <c r="J133" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H133)</f>
+        <v>1</v>
+      </c>
+      <c r="J133" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K133" s="6" t="s">
         <v>32</v>
       </c>
@@ -7806,31 +7837,31 @@
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="4" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I134" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H134)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H134)</f>
         <v>1</v>
       </c>
       <c r="J134" s="7" t="s">
@@ -7843,16 +7874,16 @@
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="4" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E135" s="6" t="s">
         <v>28</v>
@@ -7864,10 +7895,10 @@
         <v>70</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I135" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H135)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H135)</f>
         <v>1</v>
       </c>
       <c r="J135" s="7" t="s">
@@ -7880,36 +7911,34 @@
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="4" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="I136" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H136)</f>
-        <v>1</v>
-      </c>
-      <c r="J136" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H136)</f>
+        <v>1</v>
+      </c>
+      <c r="J136" s="6"/>
       <c r="K136" s="6" t="s">
         <v>32</v>
       </c>
@@ -7917,31 +7946,31 @@
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="4" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E137" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="G137" s="6" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="I137" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H137)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H137)</f>
         <v>1</v>
       </c>
       <c r="J137" s="6"/>
@@ -7952,34 +7981,36 @@
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="4" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I138" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H138)</f>
-        <v>1</v>
-      </c>
-      <c r="J138" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H138)</f>
+        <v>1</v>
+      </c>
+      <c r="J138" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K138" s="6" t="s">
         <v>32</v>
       </c>
@@ -7987,36 +8018,34 @@
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E139" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>54</v>
+        <v>395</v>
       </c>
       <c r="G139" s="6" t="s">
-        <v>55</v>
+        <v>396</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I139" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H139)</f>
-        <v>1</v>
-      </c>
-      <c r="J139" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H139)</f>
+        <v>2</v>
+      </c>
+      <c r="J139" s="6"/>
       <c r="K139" s="6" t="s">
         <v>32</v>
       </c>
@@ -8024,31 +8053,31 @@
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="4" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G140" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H140" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="D140" s="6" t="s">
-        <v>472</v>
-      </c>
-      <c r="E140" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F140" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="G140" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="H140" s="4" t="s">
-        <v>473</v>
-      </c>
       <c r="I140" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H140)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H140)</f>
         <v>2</v>
       </c>
       <c r="J140" s="6"/>
@@ -8059,7 +8088,7 @@
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="4" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>25</v>
@@ -8074,17 +8103,17 @@
         <v>28</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="G141" s="6" t="s">
-        <v>36</v>
+        <v>230</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="I141" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H141)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H141)</f>
+        <v>1</v>
       </c>
       <c r="J141" s="6"/>
       <c r="K141" s="6" t="s">
@@ -8094,31 +8123,31 @@
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="4" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="H142" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I142" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H142)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H142)</f>
         <v>1</v>
       </c>
       <c r="J142" s="6"/>
@@ -8129,31 +8158,31 @@
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="4" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E143" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>234</v>
+        <v>282</v>
       </c>
       <c r="G143" s="6" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I143" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H143)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H143)</f>
         <v>1</v>
       </c>
       <c r="J143" s="6"/>
@@ -8164,31 +8193,31 @@
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="4" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>284</v>
+        <v>92</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>284</v>
+        <v>93</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I144" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H144)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H144)</f>
         <v>1</v>
       </c>
       <c r="J144" s="6"/>
@@ -8199,31 +8228,31 @@
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="4" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E145" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="G145" s="6" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I145" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H145)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H145)</f>
         <v>1</v>
       </c>
       <c r="J145" s="6"/>
@@ -8234,31 +8263,31 @@
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="4" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I146" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H146)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H146)</f>
         <v>1</v>
       </c>
       <c r="J146" s="6"/>
@@ -8269,16 +8298,16 @@
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="4" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E147" s="6" t="s">
         <v>28</v>
@@ -8290,10 +8319,10 @@
         <v>88</v>
       </c>
       <c r="H147" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I147" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H147)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H147)</f>
         <v>1</v>
       </c>
       <c r="J147" s="6"/>
@@ -8304,31 +8333,31 @@
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="4" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>87</v>
+        <v>234</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>88</v>
+        <v>235</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="I148" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H148)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H148)</f>
         <v>1</v>
       </c>
       <c r="J148" s="6"/>
@@ -8339,31 +8368,31 @@
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="4" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E149" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>234</v>
+        <v>35</v>
       </c>
       <c r="G149" s="6" t="s">
-        <v>235</v>
+        <v>36</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I149" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H149)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H149)</f>
         <v>1</v>
       </c>
       <c r="J149" s="6"/>
@@ -8374,31 +8403,31 @@
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="I150" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H150)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H150)</f>
         <v>1</v>
       </c>
       <c r="J150" s="6"/>
@@ -8409,31 +8438,31 @@
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="4" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E151" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="G151" s="6" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I151" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H151)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H151)</f>
         <v>1</v>
       </c>
       <c r="J151" s="6"/>
@@ -8444,31 +8473,31 @@
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="4" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I152" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H152)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H152)</f>
         <v>1</v>
       </c>
       <c r="J152" s="6"/>
@@ -8479,31 +8508,31 @@
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="4" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F153" s="6" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="G153" s="6" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I153" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H153)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H153)</f>
         <v>1</v>
       </c>
       <c r="J153" s="6"/>
@@ -8514,31 +8543,31 @@
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="4" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I154" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H154)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H154)</f>
         <v>1</v>
       </c>
       <c r="J154" s="6"/>
@@ -8549,32 +8578,32 @@
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="4" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>97</v>
+        <v>192</v>
       </c>
       <c r="G155" s="6" t="s">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I155" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H155)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H155)</f>
+        <v>2</v>
       </c>
       <c r="J155" s="6"/>
       <c r="K155" s="6" t="s">
@@ -8584,31 +8613,31 @@
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="4" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B156" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C156" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G156" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H156" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="D156" s="6" t="s">
-        <v>519</v>
-      </c>
-      <c r="E156" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="G156" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="H156" s="4" t="s">
-        <v>520</v>
-      </c>
       <c r="I156" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H156)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H156)</f>
         <v>2</v>
       </c>
       <c r="J156" s="6"/>
@@ -8619,7 +8648,7 @@
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="4" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>25</v>
@@ -8634,17 +8663,17 @@
         <v>28</v>
       </c>
       <c r="F157" s="6" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="G157" s="6" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="I157" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H157)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H157)</f>
+        <v>3</v>
       </c>
       <c r="J157" s="6"/>
       <c r="K157" s="6" t="s">
@@ -8654,32 +8683,32 @@
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="4" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C158" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="G158" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="H158" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="D158" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="E158" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F158" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="G158" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="H158" s="4" t="s">
-        <v>525</v>
-      </c>
       <c r="I158" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H158)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H158)</f>
+        <v>3</v>
       </c>
       <c r="J158" s="6"/>
       <c r="K158" s="6" t="s">
@@ -8689,32 +8718,32 @@
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="4" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E159" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>159</v>
+        <v>35</v>
       </c>
       <c r="G159" s="6" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="I159" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H159)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H159)</f>
+        <v>3</v>
       </c>
       <c r="J159" s="6"/>
       <c r="K159" s="6" t="s">
@@ -8724,32 +8753,32 @@
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="4" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F160" s="6" t="s">
-        <v>530</v>
+        <v>192</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>531</v>
+        <v>193</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="I160" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H160)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H160)</f>
+        <v>1</v>
       </c>
       <c r="J160" s="6"/>
       <c r="K160" s="6" t="s">
@@ -8759,16 +8788,16 @@
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="4" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E161" s="6" t="s">
         <v>28</v>
@@ -8780,11 +8809,11 @@
         <v>36</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="I161" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H161)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H161)</f>
+        <v>1</v>
       </c>
       <c r="J161" s="6"/>
       <c r="K161" s="6" t="s">
@@ -8794,16 +8823,16 @@
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="4" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>28</v>
@@ -8815,11 +8844,11 @@
         <v>193</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="I162" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H162)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H162)</f>
+        <v>3</v>
       </c>
       <c r="J162" s="6"/>
       <c r="K162" s="6" t="s">
@@ -8829,32 +8858,32 @@
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="4" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D163" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G163" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H163" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="E163" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F163" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G163" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H163" s="4" t="s">
-        <v>539</v>
-      </c>
       <c r="I163" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H163)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H163)</f>
+        <v>3</v>
       </c>
       <c r="J163" s="6"/>
       <c r="K163" s="6" t="s">
@@ -8864,31 +8893,31 @@
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="4" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="I164" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H164)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H164)</f>
         <v>3</v>
       </c>
       <c r="J164" s="6"/>
@@ -8899,7 +8928,7 @@
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="4" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>25</v>
@@ -8914,17 +8943,17 @@
         <v>28</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="G165" s="6" t="s">
-        <v>122</v>
+        <v>36</v>
       </c>
       <c r="H165" s="4" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I165" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H165)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H165)</f>
+        <v>1</v>
       </c>
       <c r="J165" s="6"/>
       <c r="K165" s="6" t="s">
@@ -8934,34 +8963,36 @@
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="4" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>230</v>
+        <v>101</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>230</v>
+        <v>548</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="I166" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H166)</f>
-        <v>3</v>
-      </c>
-      <c r="J166" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H166)</f>
+        <v>1</v>
+      </c>
+      <c r="J166" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K166" s="6" t="s">
         <v>32</v>
       </c>
@@ -8969,34 +9000,36 @@
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="4" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E167" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>35</v>
+        <v>372</v>
       </c>
       <c r="G167" s="6" t="s">
-        <v>36</v>
+        <v>373</v>
       </c>
       <c r="H167" s="4" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="I167" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H167)</f>
-        <v>1</v>
-      </c>
-      <c r="J167" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H167)</f>
+        <v>1</v>
+      </c>
+      <c r="J167" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K167" s="6" t="s">
         <v>32</v>
       </c>
@@ -9004,36 +9037,34 @@
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="4" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>101</v>
+        <v>395</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>552</v>
+        <v>396</v>
       </c>
       <c r="H168" s="4" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="I168" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H168)</f>
-        <v>1</v>
-      </c>
-      <c r="J168" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H168)</f>
+        <v>1</v>
+      </c>
+      <c r="J168" s="6"/>
       <c r="K168" s="6" t="s">
         <v>32</v>
       </c>
@@ -9041,36 +9072,34 @@
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="4" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E169" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="G169" s="6" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="H169" s="4" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="I169" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H169)</f>
-        <v>1</v>
-      </c>
-      <c r="J169" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H169)</f>
+        <v>1</v>
+      </c>
+      <c r="J169" s="6"/>
       <c r="K169" s="6" t="s">
         <v>32</v>
       </c>
@@ -9078,34 +9107,36 @@
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="4" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>397</v>
+        <v>54</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>398</v>
+        <v>55</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="I170" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H170)</f>
-        <v>1</v>
-      </c>
-      <c r="J170" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H170)</f>
+        <v>1</v>
+      </c>
+      <c r="J170" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K170" s="6" t="s">
         <v>32</v>
       </c>
@@ -9113,34 +9144,36 @@
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="4" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E171" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>397</v>
+        <v>348</v>
       </c>
       <c r="G171" s="6" t="s">
-        <v>398</v>
+        <v>349</v>
       </c>
       <c r="H171" s="4" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="I171" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H171)</f>
-        <v>1</v>
-      </c>
-      <c r="J171" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H171)</f>
+        <v>1</v>
+      </c>
+      <c r="J171" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K171" s="6" t="s">
         <v>32</v>
       </c>
@@ -9148,36 +9181,34 @@
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="4" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>55</v>
+        <v>122</v>
       </c>
       <c r="H172" s="4" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="I172" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H172)</f>
-        <v>1</v>
-      </c>
-      <c r="J172" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H172)</f>
+        <v>1</v>
+      </c>
+      <c r="J172" s="6"/>
       <c r="K172" s="6" t="s">
         <v>32</v>
       </c>
@@ -9185,36 +9216,34 @@
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="4" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B173" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E173" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>350</v>
+        <v>87</v>
       </c>
       <c r="G173" s="6" t="s">
-        <v>351</v>
+        <v>88</v>
       </c>
       <c r="H173" s="4" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="I173" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H173)</f>
-        <v>1</v>
-      </c>
-      <c r="J173" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H173)</f>
+        <v>1</v>
+      </c>
+      <c r="J173" s="6"/>
       <c r="K173" s="6" t="s">
         <v>32</v>
       </c>
@@ -9222,31 +9251,31 @@
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="4" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B174" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="I174" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H174)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H174)</f>
         <v>1</v>
       </c>
       <c r="J174" s="6"/>
@@ -9257,31 +9286,31 @@
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="4" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B175" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E175" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="G175" s="6" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="H175" s="4" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="I175" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H175)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H175)</f>
         <v>1</v>
       </c>
       <c r="J175" s="6"/>
@@ -9292,32 +9321,32 @@
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="4" t="n">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B176" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>109</v>
+        <v>202</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>110</v>
+        <v>203</v>
       </c>
       <c r="H176" s="4" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="I176" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H176)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H176)</f>
+        <v>2</v>
       </c>
       <c r="J176" s="6"/>
       <c r="K176" s="6" t="s">
@@ -9327,32 +9356,32 @@
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="4" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B177" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D177" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F177" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="G177" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H177" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="E177" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F177" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G177" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="H177" s="4" t="s">
-        <v>580</v>
-      </c>
       <c r="I177" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H177)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H177)</f>
+        <v>2</v>
       </c>
       <c r="J177" s="6"/>
       <c r="K177" s="6" t="s">
@@ -9362,32 +9391,32 @@
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="4" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B178" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>202</v>
+        <v>49</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>203</v>
+        <v>50</v>
       </c>
       <c r="H178" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="I178" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H178)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H178)</f>
+        <v>1</v>
       </c>
       <c r="J178" s="6"/>
       <c r="K178" s="6" t="s">
@@ -9397,32 +9426,32 @@
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="4" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B179" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E179" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>230</v>
+        <v>87</v>
       </c>
       <c r="G179" s="6" t="s">
-        <v>230</v>
+        <v>88</v>
       </c>
       <c r="H179" s="4" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="I179" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H179)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H179)</f>
+        <v>1</v>
       </c>
       <c r="J179" s="6"/>
       <c r="K179" s="6" t="s">
@@ -9432,32 +9461,32 @@
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="4" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B180" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="I180" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H180)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H180)</f>
+        <v>2</v>
       </c>
       <c r="J180" s="6"/>
       <c r="K180" s="6" t="s">
@@ -9467,32 +9496,32 @@
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="4" t="n">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B181" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E181" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="G181" s="6" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I181" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H181)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H181)</f>
+        <v>2</v>
       </c>
       <c r="J181" s="6"/>
       <c r="K181" s="6" t="s">
@@ -9502,31 +9531,31 @@
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="4" t="n">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B182" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="H182" s="4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="I182" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H182)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H182)</f>
         <v>1</v>
       </c>
       <c r="J182" s="6"/>
@@ -9537,32 +9566,32 @@
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="4" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B183" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E183" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>29</v>
+        <v>230</v>
       </c>
       <c r="G183" s="6" t="s">
-        <v>30</v>
+        <v>230</v>
       </c>
       <c r="H183" s="4" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="I183" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H183)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H183)</f>
+        <v>1</v>
       </c>
       <c r="J183" s="6"/>
       <c r="K183" s="6" t="s">
@@ -9572,31 +9601,31 @@
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="4" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B184" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>121</v>
+        <v>234</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>122</v>
+        <v>235</v>
       </c>
       <c r="H184" s="4" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="I184" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H184)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H184)</f>
         <v>2</v>
       </c>
       <c r="J184" s="6"/>
@@ -9607,16 +9636,16 @@
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="4" t="n">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B185" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E185" s="6" t="s">
         <v>28</v>
@@ -9631,8 +9660,8 @@
         <v>602</v>
       </c>
       <c r="I185" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H185)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H185)</f>
+        <v>2</v>
       </c>
       <c r="J185" s="6"/>
       <c r="K185" s="6" t="s">
@@ -9642,31 +9671,31 @@
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="4" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B186" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>230</v>
+        <v>121</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>230</v>
+        <v>122</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="I186" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H186)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H186)</f>
         <v>1</v>
       </c>
       <c r="J186" s="6"/>
@@ -9677,32 +9706,32 @@
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="4" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B187" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E187" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>234</v>
+        <v>77</v>
       </c>
       <c r="G187" s="6" t="s">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="H187" s="4" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="I187" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H187)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H187)</f>
+        <v>1</v>
       </c>
       <c r="J187" s="6"/>
       <c r="K187" s="6" t="s">
@@ -9712,32 +9741,32 @@
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="4" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B188" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>121</v>
+        <v>248</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>122</v>
+        <v>248</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="I188" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H188)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H188)</f>
+        <v>1</v>
       </c>
       <c r="J188" s="6"/>
       <c r="K188" s="6" t="s">
@@ -9747,31 +9776,31 @@
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="4" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B189" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="E189" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="G189" s="6" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="I189" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H189)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H189)</f>
         <v>1</v>
       </c>
       <c r="J189" s="6"/>
@@ -9782,32 +9811,32 @@
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="4" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B190" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="H190" s="4" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="I190" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H190)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H190)</f>
+        <v>2</v>
       </c>
       <c r="J190" s="6"/>
       <c r="K190" s="6" t="s">
@@ -9817,32 +9846,32 @@
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="4" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B191" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E191" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>248</v>
+        <v>175</v>
       </c>
       <c r="G191" s="6" t="s">
-        <v>248</v>
+        <v>176</v>
       </c>
       <c r="H191" s="4" t="s">
         <v>619</v>
       </c>
       <c r="I191" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H191)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H191)</f>
+        <v>2</v>
       </c>
       <c r="J191" s="6"/>
       <c r="K191" s="6" t="s">
@@ -9852,31 +9881,31 @@
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="4" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B192" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="I192" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H192)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H192)</f>
         <v>1</v>
       </c>
       <c r="J192" s="6"/>
@@ -9887,32 +9916,32 @@
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="4" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B193" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E193" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="G193" s="6" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="H193" s="4" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="I193" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H193)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H193)</f>
+        <v>1</v>
       </c>
       <c r="J193" s="6"/>
       <c r="K193" s="6" t="s">
@@ -9922,32 +9951,32 @@
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="4" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B194" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>175</v>
+        <v>101</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="I194" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H194)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H194)</f>
+        <v>1</v>
       </c>
       <c r="J194" s="6"/>
       <c r="K194" s="6" t="s">
@@ -9957,31 +9986,31 @@
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="4" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B195" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E195" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>175</v>
+        <v>282</v>
       </c>
       <c r="G195" s="6" t="s">
-        <v>176</v>
+        <v>282</v>
       </c>
       <c r="H195" s="4" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="I195" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H195)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H195)</f>
         <v>1</v>
       </c>
       <c r="J195" s="6"/>
@@ -9992,31 +10021,31 @@
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="4" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B196" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>175</v>
+        <v>114</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="H196" s="4" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="I196" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H196)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H196)</f>
         <v>1</v>
       </c>
       <c r="J196" s="6"/>
@@ -10027,32 +10056,32 @@
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="4" t="n">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B197" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="E197" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="G197" s="6" t="s">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="H197" s="4" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="I197" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H197)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H197)</f>
+        <v>2</v>
       </c>
       <c r="J197" s="6"/>
       <c r="K197" s="6" t="s">
@@ -10062,32 +10091,32 @@
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="4" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B198" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>284</v>
+        <v>175</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>284</v>
+        <v>176</v>
       </c>
       <c r="H198" s="4" t="s">
         <v>639</v>
       </c>
       <c r="I198" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H198)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H198)</f>
+        <v>2</v>
       </c>
       <c r="J198" s="6"/>
       <c r="K198" s="6" t="s">
@@ -10097,31 +10126,31 @@
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="4" t="n">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B199" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E199" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="G199" s="6" t="s">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="H199" s="4" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="I199" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H199)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H199)</f>
         <v>1</v>
       </c>
       <c r="J199" s="6"/>
@@ -10132,32 +10161,32 @@
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="4" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B200" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>40</v>
+        <v>175</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>41</v>
+        <v>176</v>
       </c>
       <c r="H200" s="4" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="I200" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H200)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H200)</f>
+        <v>1</v>
       </c>
       <c r="J200" s="6"/>
       <c r="K200" s="6" t="s">
@@ -10167,32 +10196,32 @@
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="4" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B201" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E201" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="G201" s="6" t="s">
-        <v>176</v>
+        <v>41</v>
       </c>
       <c r="H201" s="4" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="I201" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H201)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H201)</f>
+        <v>1</v>
       </c>
       <c r="J201" s="6"/>
       <c r="K201" s="6" t="s">
@@ -10202,31 +10231,31 @@
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="4" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B202" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>40</v>
+        <v>653</v>
       </c>
       <c r="G202" s="6" t="s">
-        <v>41</v>
+        <v>654</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="I202" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H202)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H202)</f>
         <v>1</v>
       </c>
       <c r="J202" s="6"/>
@@ -10237,31 +10266,31 @@
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="4" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B203" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="E203" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>175</v>
+        <v>230</v>
       </c>
       <c r="G203" s="6" t="s">
-        <v>176</v>
+        <v>230</v>
       </c>
       <c r="H203" s="4" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="I203" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H203)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H203)</f>
         <v>1</v>
       </c>
       <c r="J203" s="6"/>
@@ -10272,31 +10301,31 @@
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="4" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B204" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>40</v>
+        <v>247</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>41</v>
+        <v>248</v>
       </c>
       <c r="H204" s="4" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="I204" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H204)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H204)</f>
         <v>1</v>
       </c>
       <c r="J204" s="6"/>
@@ -10307,31 +10336,31 @@
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="4" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B205" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="E205" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>659</v>
+        <v>101</v>
       </c>
       <c r="G205" s="6" t="s">
-        <v>660</v>
+        <v>102</v>
       </c>
       <c r="H205" s="4" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="I205" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H205)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H205)</f>
         <v>1</v>
       </c>
       <c r="J205" s="6"/>
@@ -10342,31 +10371,31 @@
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="4" t="n">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B206" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>230</v>
+        <v>175</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>230</v>
+        <v>176</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="I206" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H206)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H206)</f>
         <v>1</v>
       </c>
       <c r="J206" s="6"/>
@@ -10377,31 +10406,31 @@
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="4" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B207" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E207" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="G207" s="6" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="H207" s="4" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="I207" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H207)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H207)</f>
         <v>1</v>
       </c>
       <c r="J207" s="6"/>
@@ -10412,31 +10441,31 @@
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="4" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B208" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="I208" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H208)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H208)</f>
         <v>1</v>
       </c>
       <c r="J208" s="6"/>
@@ -10447,32 +10476,32 @@
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="4" t="n">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B209" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E209" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>175</v>
+        <v>109</v>
       </c>
       <c r="G209" s="6" t="s">
-        <v>176</v>
+        <v>110</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="I209" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H209)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H209)</f>
+        <v>2</v>
       </c>
       <c r="J209" s="6"/>
       <c r="K209" s="6" t="s">
@@ -10482,32 +10511,32 @@
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="4" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B210" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="E210" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>230</v>
+        <v>77</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>230</v>
+        <v>78</v>
       </c>
       <c r="H210" s="4" t="s">
         <v>676</v>
       </c>
       <c r="I210" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H210)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H210)</f>
+        <v>2</v>
       </c>
       <c r="J210" s="6"/>
       <c r="K210" s="6" t="s">
@@ -10517,31 +10546,31 @@
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="4" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B211" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E211" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="G211" s="6" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="I211" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H211)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H211)</f>
         <v>1</v>
       </c>
       <c r="J211" s="6"/>
@@ -10552,32 +10581,32 @@
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="4" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B212" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E212" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I212" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H212)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H212)</f>
+        <v>1</v>
       </c>
       <c r="J212" s="6"/>
       <c r="K212" s="6" t="s">
@@ -10587,34 +10616,36 @@
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="4" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E213" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="G213" s="6" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H213" s="4" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="I213" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H213)</f>
-        <v>2</v>
-      </c>
-      <c r="J213" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H213)</f>
+        <v>1</v>
+      </c>
+      <c r="J213" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K213" s="6" t="s">
         <v>32</v>
       </c>
@@ -10622,34 +10653,36 @@
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="4" t="n">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B214" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E214" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="H214" s="4" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="I214" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H214)</f>
-        <v>1</v>
-      </c>
-      <c r="J214" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H214)</f>
+        <v>1</v>
+      </c>
+      <c r="J214" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K214" s="6" t="s">
         <v>32</v>
       </c>
@@ -10657,31 +10690,31 @@
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="4" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B215" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E215" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="G215" s="6" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="H215" s="4" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="I215" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H215)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H215)</f>
         <v>1</v>
       </c>
       <c r="J215" s="6"/>
@@ -10692,36 +10725,34 @@
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="4" t="n">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B216" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="E216" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="H216" s="4" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="I216" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H216)</f>
-        <v>1</v>
-      </c>
-      <c r="J216" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H216)</f>
+        <v>1</v>
+      </c>
+      <c r="J216" s="6"/>
       <c r="K216" s="6" t="s">
         <v>32</v>
       </c>
@@ -10729,7 +10760,7 @@
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="4" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>25</v>
@@ -10738,27 +10769,25 @@
         <v>694</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E217" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>54</v>
+        <v>372</v>
       </c>
       <c r="G217" s="6" t="s">
-        <v>55</v>
+        <v>373</v>
       </c>
       <c r="H217" s="4" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="I217" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H217)</f>
-        <v>1</v>
-      </c>
-      <c r="J217" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H217)</f>
+        <v>1</v>
+      </c>
+      <c r="J217" s="6"/>
       <c r="K217" s="6" t="s">
         <v>32</v>
       </c>
@@ -10766,34 +10795,36 @@
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="4" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E218" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="G218" s="6" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="H218" s="4" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="I218" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H218)</f>
-        <v>1</v>
-      </c>
-      <c r="J218" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H218)</f>
+        <v>1</v>
+      </c>
+      <c r="J218" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K218" s="6" t="s">
         <v>32</v>
       </c>
@@ -10801,31 +10832,31 @@
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="4" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E219" s="6" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="F219" s="6" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="G219" s="6" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="H219" s="4" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="I219" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H219)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H219)</f>
         <v>1</v>
       </c>
       <c r="J219" s="6"/>
@@ -10836,16 +10867,16 @@
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="4" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B220" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="E220" s="6" t="s">
         <v>28</v>
@@ -10857,10 +10888,10 @@
         <v>88</v>
       </c>
       <c r="H220" s="4" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="I220" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H220)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H220)</f>
         <v>1</v>
       </c>
       <c r="J220" s="6"/>
@@ -10871,36 +10902,34 @@
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="4" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="E221" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F221" s="6" t="s">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="G221" s="6" t="s">
-        <v>83</v>
+        <v>527</v>
       </c>
       <c r="H221" s="4" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="I221" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H221)</f>
-        <v>1</v>
-      </c>
-      <c r="J221" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H221)</f>
+        <v>1</v>
+      </c>
+      <c r="J221" s="6"/>
       <c r="K221" s="6" t="s">
         <v>32</v>
       </c>
@@ -10908,31 +10937,31 @@
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="4" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B222" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F222" s="6" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="G222" s="6" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="I222" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H222)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H222)</f>
         <v>1</v>
       </c>
       <c r="J222" s="6"/>
@@ -10943,32 +10972,32 @@
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="4" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="E223" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F223" s="6" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="G223" s="6" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="I223" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H223)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H223)</f>
+        <v>2</v>
       </c>
       <c r="J223" s="6"/>
       <c r="K223" s="6" t="s">
@@ -10978,32 +11007,32 @@
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="4" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B224" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="E224" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F224" s="6" t="s">
-        <v>530</v>
+        <v>282</v>
       </c>
       <c r="G224" s="6" t="s">
-        <v>531</v>
+        <v>282</v>
       </c>
       <c r="H224" s="4" t="s">
         <v>716</v>
       </c>
       <c r="I224" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H224)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H224)</f>
+        <v>2</v>
       </c>
       <c r="J224" s="6"/>
       <c r="K224" s="6" t="s">
@@ -11013,31 +11042,31 @@
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="4" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E225" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F225" s="6" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="G225" s="6" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="I225" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H225)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H225)</f>
         <v>1</v>
       </c>
       <c r="J225" s="6"/>
@@ -11048,32 +11077,32 @@
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="4" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B226" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E226" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F226" s="6" t="s">
-        <v>159</v>
+        <v>97</v>
       </c>
       <c r="G226" s="6" t="s">
-        <v>160</v>
+        <v>97</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="I226" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H226)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H226)</f>
+        <v>1</v>
       </c>
       <c r="J226" s="6"/>
       <c r="K226" s="6" t="s">
@@ -11083,32 +11112,32 @@
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="4" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E227" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F227" s="6" t="s">
-        <v>284</v>
+        <v>727</v>
       </c>
       <c r="G227" s="6" t="s">
-        <v>284</v>
+        <v>728</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="I227" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H227)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H227)</f>
+        <v>1</v>
       </c>
       <c r="J227" s="6"/>
       <c r="K227" s="6" t="s">
@@ -11118,31 +11147,31 @@
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="4" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="E228" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F228" s="6" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G228" s="6" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="I228" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H228)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H228)</f>
         <v>1</v>
       </c>
       <c r="J228" s="6"/>
@@ -11153,34 +11182,36 @@
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="4" t="n">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B229" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="E229" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F229" s="6" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="G229" s="6" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="H229" s="4" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="I229" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H229)</f>
-        <v>1</v>
-      </c>
-      <c r="J229" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H229)</f>
+        <v>1</v>
+      </c>
+      <c r="J229" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K229" s="6" t="s">
         <v>32</v>
       </c>
@@ -11188,34 +11219,36 @@
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="4" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B230" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="E230" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F230" s="6" t="s">
-        <v>733</v>
+        <v>54</v>
       </c>
       <c r="G230" s="6" t="s">
-        <v>734</v>
+        <v>55</v>
       </c>
       <c r="H230" s="4" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="I230" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H230)</f>
-        <v>1</v>
-      </c>
-      <c r="J230" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H230)</f>
+        <v>1</v>
+      </c>
+      <c r="J230" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K230" s="6" t="s">
         <v>32</v>
       </c>
@@ -11223,34 +11256,36 @@
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="4" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B231" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="E231" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F231" s="6" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="G231" s="6" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H231" s="4" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="I231" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H231)</f>
-        <v>1</v>
-      </c>
-      <c r="J231" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H231)</f>
+        <v>1</v>
+      </c>
+      <c r="J231" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K231" s="6" t="s">
         <v>32</v>
       </c>
@@ -11258,31 +11293,31 @@
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="4" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B232" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="E232" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F232" s="6" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="G232" s="6" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="I232" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H232)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H232)</f>
         <v>1</v>
       </c>
       <c r="J232" s="7" t="s">
@@ -11295,36 +11330,34 @@
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="4" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="E233" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F233" s="6" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="G233" s="6" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="H233" s="4" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="I233" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H233)</f>
-        <v>1</v>
-      </c>
-      <c r="J233" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H233)</f>
+        <v>3</v>
+      </c>
+      <c r="J233" s="6"/>
       <c r="K233" s="6" t="s">
         <v>32</v>
       </c>
@@ -11332,36 +11365,34 @@
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="4" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B234" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="E234" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F234" s="6" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="G234" s="6" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
       <c r="H234" s="4" t="s">
         <v>747</v>
       </c>
       <c r="I234" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H234)</f>
-        <v>1</v>
-      </c>
-      <c r="J234" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H234)</f>
+        <v>3</v>
+      </c>
+      <c r="J234" s="6"/>
       <c r="K234" s="6" t="s">
         <v>32</v>
       </c>
@@ -11369,36 +11400,34 @@
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="4" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E235" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F235" s="6" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G235" s="6" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H235" s="4" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="I235" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H235)</f>
-        <v>1</v>
-      </c>
-      <c r="J235" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H235)</f>
+        <v>3</v>
+      </c>
+      <c r="J235" s="6"/>
       <c r="K235" s="6" t="s">
         <v>32</v>
       </c>
@@ -11406,34 +11435,34 @@
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="4" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B236" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E236" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F236" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G236" s="6" t="s">
-        <v>97</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="G236" s="6"/>
       <c r="H236" s="4" t="s">
         <v>753</v>
       </c>
       <c r="I236" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H236)</f>
-        <v>3</v>
-      </c>
-      <c r="J236" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H236)</f>
+        <v>2</v>
+      </c>
+      <c r="J236" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K236" s="6" t="s">
         <v>32</v>
       </c>
@@ -11441,16 +11470,16 @@
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="4" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C237" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="D237" s="6" t="s">
         <v>754</v>
-      </c>
-      <c r="D237" s="6" t="s">
-        <v>755</v>
       </c>
       <c r="E237" s="6" t="s">
         <v>28</v>
@@ -11465,8 +11494,8 @@
         <v>753</v>
       </c>
       <c r="I237" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H237)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H237)</f>
+        <v>2</v>
       </c>
       <c r="J237" s="6"/>
       <c r="K237" s="6" t="s">
@@ -11476,32 +11505,32 @@
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="4" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B238" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C238" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="D238" s="6" t="s">
         <v>756</v>
       </c>
-      <c r="D238" s="6" t="s">
+      <c r="E238" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F238" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G238" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="H238" s="4" t="s">
         <v>757</v>
       </c>
-      <c r="E238" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F238" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G238" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H238" s="4" t="s">
-        <v>753</v>
-      </c>
       <c r="I238" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H238)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H238)</f>
+        <v>1</v>
       </c>
       <c r="J238" s="6"/>
       <c r="K238" s="6" t="s">
@@ -11511,7 +11540,7 @@
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="4" t="n">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>25</v>
@@ -11526,14 +11555,16 @@
         <v>28</v>
       </c>
       <c r="F239" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G239" s="6"/>
+        <v>40</v>
+      </c>
+      <c r="G239" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="H239" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="I239" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H239)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H239)</f>
         <v>2</v>
       </c>
       <c r="J239" s="7" t="s">
@@ -11546,34 +11577,36 @@
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="4" t="n">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="D240" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="E240" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F240" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="G240" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="H240" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="E240" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F240" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="G240" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="H240" s="4" t="s">
-        <v>759</v>
-      </c>
       <c r="I240" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H240)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H240)</f>
         <v>2</v>
       </c>
-      <c r="J240" s="6"/>
+      <c r="J240" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K240" s="6" t="s">
         <v>32</v>
       </c>
@@ -11581,31 +11614,31 @@
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="4" t="n">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B241" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="E241" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="G241" s="6" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="H241" s="4" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="I241" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H241)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H241)</f>
         <v>1</v>
       </c>
       <c r="J241" s="6"/>
@@ -11616,36 +11649,34 @@
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="4" t="n">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B242" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="E242" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F242" s="6" t="s">
-        <v>40</v>
+        <v>395</v>
       </c>
       <c r="G242" s="6" t="s">
-        <v>41</v>
+        <v>396</v>
       </c>
       <c r="H242" s="4" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="I242" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H242)</f>
-        <v>2</v>
-      </c>
-      <c r="J242" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H242)</f>
+        <v>1</v>
+      </c>
+      <c r="J242" s="6"/>
       <c r="K242" s="6" t="s">
         <v>32</v>
       </c>
@@ -11653,36 +11684,34 @@
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="4" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="E243" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F243" s="6" t="s">
-        <v>350</v>
+        <v>69</v>
       </c>
       <c r="G243" s="6" t="s">
-        <v>351</v>
+        <v>70</v>
       </c>
       <c r="H243" s="4" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="I243" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H243)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H243)</f>
         <v>2</v>
       </c>
-      <c r="J243" s="7" t="s">
-        <v>57</v>
-      </c>
+      <c r="J243" s="6"/>
       <c r="K243" s="6" t="s">
         <v>32</v>
       </c>
@@ -11690,7 +11719,7 @@
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="4" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>25</v>
@@ -11705,19 +11734,21 @@
         <v>28</v>
       </c>
       <c r="F244" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="G244" s="6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H244" s="4" t="s">
         <v>771</v>
       </c>
       <c r="I244" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H244)</f>
-        <v>1</v>
-      </c>
-      <c r="J244" s="6"/>
+        <f aca="false">COUNTIF($H$3:$H$248,H244)</f>
+        <v>2</v>
+      </c>
+      <c r="J244" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="K244" s="6" t="s">
         <v>32</v>
       </c>
@@ -11725,7 +11756,7 @@
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="4" t="n">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>25</v>
@@ -11740,16 +11771,16 @@
         <v>28</v>
       </c>
       <c r="F245" s="6" t="s">
-        <v>397</v>
+        <v>526</v>
       </c>
       <c r="G245" s="6" t="s">
-        <v>398</v>
+        <v>527</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>774</v>
       </c>
       <c r="I245" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H245)</f>
+        <f aca="false">COUNTIF($H$3:$H$248,H245)</f>
         <v>1</v>
       </c>
       <c r="J245" s="6"/>
@@ -11760,7 +11791,7 @@
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="4" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B246" s="5" t="s">
         <v>25</v>
@@ -11775,17 +11806,17 @@
         <v>28</v>
       </c>
       <c r="F246" s="6" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="G246" s="6" t="s">
-        <v>70</v>
+        <v>193</v>
       </c>
       <c r="H246" s="4" t="s">
         <v>777</v>
       </c>
       <c r="I246" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H246)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H246)</f>
+        <v>3</v>
       </c>
       <c r="J246" s="6"/>
       <c r="K246" s="6" t="s">
@@ -11795,36 +11826,34 @@
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="4" t="n">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="E247" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F247" s="6" t="s">
-        <v>69</v>
+        <v>285</v>
       </c>
       <c r="G247" s="6" t="s">
-        <v>70</v>
+        <v>286</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>777</v>
       </c>
       <c r="I247" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H247)</f>
-        <v>2</v>
-      </c>
-      <c r="J247" s="7" t="s">
-        <v>57</v>
-      </c>
+        <f aca="false">COUNTIF($H$3:$H$248,H247)</f>
+        <v>3</v>
+      </c>
+      <c r="J247" s="6"/>
       <c r="K247" s="6" t="s">
         <v>32</v>
       </c>
@@ -11832,32 +11861,32 @@
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="4" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B248" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E248" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F248" s="6" t="s">
-        <v>530</v>
+        <v>285</v>
       </c>
       <c r="G248" s="6" t="s">
-        <v>531</v>
+        <v>286</v>
       </c>
       <c r="H248" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="I248" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H248)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF($H$3:$H$248,H248)</f>
+        <v>3</v>
       </c>
       <c r="J248" s="6"/>
       <c r="K248" s="6" t="s">
@@ -11865,126 +11894,165 @@
       </c>
       <c r="L248" s="4"/>
     </row>
-    <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A249" s="4" t="n">
-        <v>352</v>
-      </c>
-      <c r="B249" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C249" s="6" t="s">
-        <v>781</v>
-      </c>
-      <c r="D249" s="6" t="s">
+    <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="8" t="n">
+        <v>247</v>
+      </c>
+      <c r="B249" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C249" s="10" t="s">
         <v>782</v>
       </c>
-      <c r="E249" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F249" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="G249" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="H249" s="4" t="s">
+      <c r="D249" s="10" t="s">
         <v>783</v>
       </c>
-      <c r="I249" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H249)</f>
-        <v>3</v>
-      </c>
-      <c r="J249" s="6"/>
-      <c r="K249" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L249" s="4"/>
-    </row>
-    <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A250" s="4" t="n">
-        <v>353</v>
-      </c>
-      <c r="B250" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C250" s="6" t="s">
+      <c r="E249" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F249" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="G249" s="10" t="s">
         <v>784</v>
       </c>
-      <c r="D250" s="6" t="s">
+      <c r="H249" s="8" t="s">
         <v>785</v>
       </c>
-      <c r="E250" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F250" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G250" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="H250" s="4" t="s">
-        <v>783</v>
-      </c>
-      <c r="I250" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H250)</f>
-        <v>3</v>
-      </c>
-      <c r="J250" s="6"/>
-      <c r="K250" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L250" s="4"/>
-    </row>
-    <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A251" s="4" t="n">
-        <v>354</v>
-      </c>
-      <c r="B251" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C251" s="6" t="s">
+      <c r="I249" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J249" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K249" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L249" s="8"/>
+    </row>
+    <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="8" t="n">
+        <v>248</v>
+      </c>
+      <c r="B250" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C250" s="10" t="s">
         <v>786</v>
       </c>
-      <c r="D251" s="6" t="s">
+      <c r="D250" s="10" t="s">
         <v>787</v>
       </c>
-      <c r="E251" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F251" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G251" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="H251" s="4" t="s">
-        <v>783</v>
-      </c>
-      <c r="I251" s="4" t="n">
-        <f aca="false">COUNTIF($H$3:$H$251,H251)</f>
-        <v>3</v>
-      </c>
-      <c r="J251" s="6"/>
-      <c r="K251" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L251" s="4"/>
+      <c r="E250" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F250" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="G250" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="H250" s="8" t="s">
+        <v>788</v>
+      </c>
+      <c r="I250" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J250" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K250" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L250" s="8"/>
+    </row>
+    <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="8" t="n">
+        <v>249</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C251" s="10" t="s">
+        <v>789</v>
+      </c>
+      <c r="D251" s="10" t="s">
+        <v>790</v>
+      </c>
+      <c r="E251" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F251" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="G251" s="10" t="s">
+        <v>791</v>
+      </c>
+      <c r="H251" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="I251" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J251" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K251" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L251" s="8"/>
+    </row>
+    <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="B252" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C252" s="10" t="s">
+        <v>793</v>
+      </c>
+      <c r="D252" s="10" t="s">
+        <v>794</v>
+      </c>
+      <c r="E252" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F252" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G252" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H252" s="8" t="s">
+        <v>795</v>
+      </c>
+      <c r="I252" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J252" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K252" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L252" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:L251"/>
+  <autoFilter ref="A2:L248"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F3:F251" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F3:F248" type="list">
       <formula1>"Biblical Teaching,Christian 80's,Christian Alternative R&amp;B,Christian Bluegrass,Christian Blues-Jazz,Christian Bounce Drop,Christian Chillwave,Christian Country,Christian Country - Pop,Christian Dance,Christian EDM,Christian Hip-Hop,Christian K-Pop,Christi"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J3:J251" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J3:J248" type="list">
       <formula1>"NEW,"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K3:K251" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K3:K248" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -12239,6 +12307,7 @@
     <hyperlink ref="B249" r:id="rId247" display="▶ Play"/>
     <hyperlink ref="B250" r:id="rId248" display="▶ Play"/>
     <hyperlink ref="B251" r:id="rId249" display="▶ Play"/>
+    <hyperlink ref="B252" r:id="rId250" display="▶ Play"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12247,7 +12316,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId250"/>
+  <drawing r:id="rId251"/>
 </worksheet>
 </file>
 
@@ -12266,90 +12335,90 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>791</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>792</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>793</v>
+      <c r="A2" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>800</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>794</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>795</v>
+      <c r="A3" s="12" t="s">
+        <v>802</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>803</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>796</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>797</v>
+      <c r="A4" s="12" t="s">
+        <v>804</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>798</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>799</v>
+      <c r="A5" s="12" t="s">
+        <v>806</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>800</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>801</v>
+      <c r="A6" s="12" t="s">
+        <v>808</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>809</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>802</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>803</v>
+      <c r="A7" s="12" t="s">
+        <v>810</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>804</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>805</v>
+      <c r="A8" s="12" t="s">
+        <v>812</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>813</v>
       </c>
     </row>
   </sheetData>
@@ -12379,24 +12448,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="B2" s="6" t="n">
         <v>0</v>
@@ -12405,13 +12474,13 @@
         <v>6</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="E2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>6</v>
@@ -12420,15 +12489,15 @@
         <v>10</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>10</v>
@@ -12437,15 +12506,15 @@
         <v>14</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>818</v>
+        <v>791</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>14</v>
@@ -12454,15 +12523,15 @@
         <v>17</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>17</v>
@@ -12471,13 +12540,13 @@
         <v>20</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>20</v>
@@ -12486,10 +12555,10 @@
         <v>24</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
     </row>
   </sheetData>
@@ -12521,405 +12590,405 @@
         <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A2)</f>
+      <c r="B2" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A2)</f>
         <v>9</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>827</v>
+      <c r="C2" s="8" t="s">
+        <v>834</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A3)</f>
+      <c r="B3" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A3)</f>
         <v>3</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>827</v>
+      <c r="C3" s="8" t="s">
+        <v>834</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="B4" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A4)</f>
+      <c r="B4" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A4)</f>
         <v>7</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="B5" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A5)</f>
+      <c r="B5" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A5)</f>
+        <v>9</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="B6" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A6)</f>
+        <v>4</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A7)</f>
+        <v>3</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A8)</f>
+        <v>4</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A9)</f>
+        <v>12</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A10)</f>
+        <v>5</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A11)</f>
         <v>10</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="B6" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A6)</f>
+      <c r="C11" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="B12" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A12)</f>
+        <v>6</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A13)</f>
+        <v>7</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A14)</f>
+        <v>25</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A15)</f>
+        <v>11</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A16)</f>
+        <v>9</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="B17" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A17)</f>
+        <v>4</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A18)</f>
+        <v>13</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A19)</f>
+        <v>14</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A20)</f>
+        <v>6</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="B21" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A21)</f>
+        <v>1</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="B22" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A22)</f>
+        <v>1</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="B23" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A23)</f>
         <v>3</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A7)</f>
+      <c r="C23" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A24)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="B25" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A25)</f>
         <v>3</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="B8" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A8)</f>
-        <v>5</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A9)</f>
-        <v>15</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="B10" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A10)</f>
-        <v>5</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B11" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A11)</f>
-        <v>14</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="B12" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A12)</f>
+      <c r="C25" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A26)</f>
+        <v>9</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A27)</f>
+        <v>12</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="B28" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A28)</f>
         <v>6</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A13)</f>
-        <v>7</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A14)</f>
-        <v>25</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B15" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A15)</f>
+      <c r="C28" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A29)</f>
+        <v>8</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A30)</f>
+        <v>8</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B31" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A31)</f>
         <v>10</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="B16" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A16)</f>
-        <v>9</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="B17" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A17)</f>
-        <v>4</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A18)</f>
-        <v>12</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A19)</f>
-        <v>14</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B20" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A20)</f>
+      <c r="C31" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B32" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A32)</f>
+        <v>1</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B33" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A33)</f>
+        <v>2</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="8" t="n">
+        <f aca="false">COUNTIF('Song Library'!$F$3:$F$248,A34)</f>
         <v>6</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>659</v>
-      </c>
-      <c r="B21" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A21)</f>
-        <v>1</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
-        <v>733</v>
-      </c>
-      <c r="B22" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A22)</f>
-        <v>1</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="B23" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A23)</f>
-        <v>3</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A24)</f>
-        <v>15</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="B25" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A25)</f>
-        <v>3</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="B26" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A26)</f>
-        <v>9</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B27" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A27)</f>
-        <v>12</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="B28" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A28)</f>
-        <v>6</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A29)</f>
-        <v>8</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="B30" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A30)</f>
-        <v>5</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="B31" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A31)</f>
-        <v>10</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="B32" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A32)</f>
-        <v>1</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="B33" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A33)</f>
-        <v>2</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="10" t="n">
-        <f aca="false">COUNTIF('Song Library'!$F$3:$F$251,A34)</f>
-        <v>6</v>
-      </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="8" t="s">
         <v>32</v>
       </c>
     </row>

--- a/Refined_Radio_Control.xlsx
+++ b/Refined_Radio_Control.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Genres" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Song Library'!$A$2:$L$248</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Song Library'!$A$2:$L$259</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="858">
   <si>
     <t xml:space="preserve">REFINED RADIO — MASTER CONTROL SHEET</t>
   </si>
@@ -2417,6 +2417,72 @@
     <t xml:space="preserve">Awoken the Master</t>
   </si>
   <si>
+    <t xml:space="preserve">music/Sweet Release (Chill).mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweet Release (Chill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweet Release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">music/He Strengthens Me (Alternative 2000s Rock).mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He Strengthens Me (Alt Rock)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He Strengthens Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">music/Shine His Light (K -Pop).mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shine His Light (K-Pop)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shine His Light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">music/I Can Count on You (Country).mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Can Count on You (Country)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Can Count on You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">music/What Must I Do (2000s Alternative Metal).mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What Must I Do (Alt Rock)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What Must I Do</t>
+  </si>
+  <si>
+    <t xml:space="preserve">music/One Promise (R&amp;B).mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One Promise (R&amp;B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One Promise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">music/Boots-A-Stompin’ (For the King) (Country).mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boots-A-Stompin’ (For the King) (Country)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boots-A-Stompin’</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rule</t>
   </si>
   <si>
@@ -2438,7 +2504,7 @@
     <t xml:space="preserve">Play-all rotation</t>
   </si>
   <si>
-    <t xml:space="preserve">Whole catalog plays before repeats.</t>
+    <t xml:space="preserve">Every song is always eligible; the whole catalog cycles before anything repeats.</t>
   </si>
   <si>
     <t xml:space="preserve">No immediate repeat</t>
@@ -2468,7 +2534,10 @@
     <t xml:space="preserve">Follow daypart clock</t>
   </si>
   <si>
-    <t xml:space="preserve">Covered genres play in their dayparts.</t>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OFF — full play-all: every song airs at any hour (dayparts no longer gate the music).</t>
   </si>
   <si>
     <t xml:space="preserve">Daypart Name</t>
@@ -3132,10 +3201,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
+  <sheetPr filterMode="true">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L252"/>
+  <dimension ref="A1:L259"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3206,7 +3275,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="n">
         <v>1</v>
       </c>
@@ -3241,7 +3310,7 @@
       </c>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
@@ -3276,7 +3345,7 @@
       </c>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="n">
         <v>3</v>
       </c>
@@ -3311,7 +3380,7 @@
       </c>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="n">
         <v>4</v>
       </c>
@@ -3346,7 +3415,7 @@
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="n">
         <v>5</v>
       </c>
@@ -3455,7 +3524,7 @@
       </c>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="n">
         <v>8</v>
       </c>
@@ -3490,7 +3559,7 @@
       </c>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="n">
         <v>9</v>
       </c>
@@ -3525,7 +3594,7 @@
       </c>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="n">
         <v>10</v>
       </c>
@@ -3560,7 +3629,7 @@
       </c>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="n">
         <v>11</v>
       </c>
@@ -3595,7 +3664,7 @@
       </c>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
@@ -3667,7 +3736,7 @@
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="n">
         <v>17</v>
       </c>
@@ -3739,7 +3808,7 @@
       </c>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="n">
         <v>22</v>
       </c>
@@ -3774,7 +3843,7 @@
       </c>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="n">
         <v>23</v>
       </c>
@@ -3809,7 +3878,7 @@
       </c>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="n">
         <v>25</v>
       </c>
@@ -3881,7 +3950,7 @@
       </c>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="n">
         <v>27</v>
       </c>
@@ -3916,7 +3985,7 @@
       </c>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="n">
         <v>29</v>
       </c>
@@ -3951,7 +4020,7 @@
       </c>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="n">
         <v>30</v>
       </c>
@@ -3986,7 +4055,7 @@
       </c>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="n">
         <v>32</v>
       </c>
@@ -4021,7 +4090,7 @@
       </c>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="n">
         <v>36</v>
       </c>
@@ -4056,7 +4125,7 @@
       </c>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="n">
         <v>38</v>
       </c>
@@ -4091,7 +4160,7 @@
       </c>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="n">
         <v>40</v>
       </c>
@@ -4126,7 +4195,7 @@
       </c>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="n">
         <v>42</v>
       </c>
@@ -4198,7 +4267,7 @@
       </c>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
         <v>44</v>
       </c>
@@ -4233,7 +4302,7 @@
       </c>
       <c r="L31" s="4"/>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="n">
         <v>45</v>
       </c>
@@ -4268,7 +4337,7 @@
       </c>
       <c r="L32" s="4"/>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="n">
         <v>46</v>
       </c>
@@ -4303,7 +4372,7 @@
       </c>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="n">
         <v>47</v>
       </c>
@@ -4338,7 +4407,7 @@
       </c>
       <c r="L34" s="4"/>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="n">
         <v>48</v>
       </c>
@@ -4373,7 +4442,7 @@
       </c>
       <c r="L35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="n">
         <v>50</v>
       </c>
@@ -4408,7 +4477,7 @@
       </c>
       <c r="L36" s="4"/>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="n">
         <v>51</v>
       </c>
@@ -4443,7 +4512,7 @@
       </c>
       <c r="L37" s="4"/>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="n">
         <v>52</v>
       </c>
@@ -4478,7 +4547,7 @@
       </c>
       <c r="L38" s="4"/>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="n">
         <v>54</v>
       </c>
@@ -4513,7 +4582,7 @@
       </c>
       <c r="L39" s="4"/>
     </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="n">
         <v>56</v>
       </c>
@@ -4548,7 +4617,7 @@
       </c>
       <c r="L40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="n">
         <v>60</v>
       </c>
@@ -4583,7 +4652,7 @@
       </c>
       <c r="L41" s="4"/>
     </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="n">
         <v>61</v>
       </c>
@@ -4692,7 +4761,7 @@
       </c>
       <c r="L44" s="4"/>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="n">
         <v>65</v>
       </c>
@@ -4727,7 +4796,7 @@
       </c>
       <c r="L45" s="4"/>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="n">
         <v>66</v>
       </c>
@@ -4762,7 +4831,7 @@
       </c>
       <c r="L46" s="4"/>
     </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="n">
         <v>67</v>
       </c>
@@ -4797,7 +4866,7 @@
       </c>
       <c r="L47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="n">
         <v>68</v>
       </c>
@@ -4832,7 +4901,7 @@
       </c>
       <c r="L48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="n">
         <v>69</v>
       </c>
@@ -4867,7 +4936,7 @@
       </c>
       <c r="L49" s="4"/>
     </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="n">
         <v>70</v>
       </c>
@@ -4902,7 +4971,7 @@
       </c>
       <c r="L50" s="4"/>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="n">
         <v>73</v>
       </c>
@@ -4937,7 +5006,7 @@
       </c>
       <c r="L51" s="4"/>
     </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="n">
         <v>74</v>
       </c>
@@ -4972,7 +5041,7 @@
       </c>
       <c r="L52" s="4"/>
     </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="n">
         <v>77</v>
       </c>
@@ -5007,7 +5076,7 @@
       </c>
       <c r="L53" s="4"/>
     </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="n">
         <v>78</v>
       </c>
@@ -5042,7 +5111,7 @@
       </c>
       <c r="L54" s="4"/>
     </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="n">
         <v>79</v>
       </c>
@@ -5077,7 +5146,7 @@
       </c>
       <c r="L55" s="4"/>
     </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="n">
         <v>81</v>
       </c>
@@ -5112,7 +5181,7 @@
       </c>
       <c r="L56" s="4"/>
     </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="n">
         <v>84</v>
       </c>
@@ -5147,7 +5216,7 @@
       </c>
       <c r="L57" s="4"/>
     </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="n">
         <v>85</v>
       </c>
@@ -5182,7 +5251,7 @@
       </c>
       <c r="L58" s="4"/>
     </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="n">
         <v>86</v>
       </c>
@@ -5217,7 +5286,7 @@
       </c>
       <c r="L59" s="4"/>
     </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="n">
         <v>89</v>
       </c>
@@ -5252,7 +5321,7 @@
       </c>
       <c r="L60" s="4"/>
     </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="n">
         <v>91</v>
       </c>
@@ -5287,7 +5356,7 @@
       </c>
       <c r="L61" s="4"/>
     </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="n">
         <v>92</v>
       </c>
@@ -5359,7 +5428,7 @@
       </c>
       <c r="L63" s="4"/>
     </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="n">
         <v>96</v>
       </c>
@@ -5394,7 +5463,7 @@
       </c>
       <c r="L64" s="4"/>
     </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="n">
         <v>98</v>
       </c>
@@ -5429,7 +5498,7 @@
       </c>
       <c r="L65" s="4"/>
     </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="n">
         <v>102</v>
       </c>
@@ -5464,7 +5533,7 @@
       </c>
       <c r="L66" s="4"/>
     </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="n">
         <v>103</v>
       </c>
@@ -5536,7 +5605,7 @@
       </c>
       <c r="L68" s="4"/>
     </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="n">
         <v>105</v>
       </c>
@@ -5571,7 +5640,7 @@
       </c>
       <c r="L69" s="4"/>
     </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="n">
         <v>107</v>
       </c>
@@ -5606,7 +5675,7 @@
       </c>
       <c r="L70" s="4"/>
     </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="n">
         <v>108</v>
       </c>
@@ -5641,7 +5710,7 @@
       </c>
       <c r="L71" s="4"/>
     </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="n">
         <v>109</v>
       </c>
@@ -5676,7 +5745,7 @@
       </c>
       <c r="L72" s="4"/>
     </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="n">
         <v>111</v>
       </c>
@@ -5711,7 +5780,7 @@
       </c>
       <c r="L73" s="4"/>
     </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="n">
         <v>113</v>
       </c>
@@ -5746,7 +5815,7 @@
       </c>
       <c r="L74" s="4"/>
     </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="n">
         <v>114</v>
       </c>
@@ -5781,7 +5850,7 @@
       </c>
       <c r="L75" s="4"/>
     </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="n">
         <v>116</v>
       </c>
@@ -5816,7 +5885,7 @@
       </c>
       <c r="L76" s="4"/>
     </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="n">
         <v>118</v>
       </c>
@@ -5851,7 +5920,7 @@
       </c>
       <c r="L77" s="4"/>
     </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="n">
         <v>119</v>
       </c>
@@ -5886,7 +5955,7 @@
       </c>
       <c r="L78" s="4"/>
     </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="n">
         <v>124</v>
       </c>
@@ -5921,7 +5990,7 @@
       </c>
       <c r="L79" s="4"/>
     </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="n">
         <v>125</v>
       </c>
@@ -5956,7 +6025,7 @@
       </c>
       <c r="L80" s="4"/>
     </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="n">
         <v>126</v>
       </c>
@@ -5991,7 +6060,7 @@
       </c>
       <c r="L81" s="4"/>
     </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="n">
         <v>131</v>
       </c>
@@ -6026,7 +6095,7 @@
       </c>
       <c r="L82" s="4"/>
     </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="n">
         <v>132</v>
       </c>
@@ -6061,7 +6130,7 @@
       </c>
       <c r="L83" s="4"/>
     </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="n">
         <v>135</v>
       </c>
@@ -6096,7 +6165,7 @@
       </c>
       <c r="L84" s="4"/>
     </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="n">
         <v>136</v>
       </c>
@@ -6131,7 +6200,7 @@
       </c>
       <c r="L85" s="4"/>
     </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="n">
         <v>137</v>
       </c>
@@ -6166,7 +6235,7 @@
       </c>
       <c r="L86" s="4"/>
     </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="n">
         <v>138</v>
       </c>
@@ -6201,7 +6270,7 @@
       </c>
       <c r="L87" s="4"/>
     </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="n">
         <v>139</v>
       </c>
@@ -6236,7 +6305,7 @@
       </c>
       <c r="L88" s="4"/>
     </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="n">
         <v>140</v>
       </c>
@@ -6308,7 +6377,7 @@
       </c>
       <c r="L90" s="4"/>
     </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="n">
         <v>145</v>
       </c>
@@ -6343,7 +6412,7 @@
       </c>
       <c r="L91" s="4"/>
     </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="n">
         <v>146</v>
       </c>
@@ -6415,7 +6484,7 @@
       </c>
       <c r="L93" s="4"/>
     </row>
-    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="n">
         <v>148</v>
       </c>
@@ -6450,7 +6519,7 @@
       </c>
       <c r="L94" s="4"/>
     </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="n">
         <v>149</v>
       </c>
@@ -6485,7 +6554,7 @@
       </c>
       <c r="L95" s="4"/>
     </row>
-    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="n">
         <v>152</v>
       </c>
@@ -6520,7 +6589,7 @@
       </c>
       <c r="L96" s="4"/>
     </row>
-    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="n">
         <v>153</v>
       </c>
@@ -6629,7 +6698,7 @@
       </c>
       <c r="L99" s="4"/>
     </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="n">
         <v>158</v>
       </c>
@@ -6664,7 +6733,7 @@
       </c>
       <c r="L100" s="4"/>
     </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="n">
         <v>160</v>
       </c>
@@ -6699,7 +6768,7 @@
       </c>
       <c r="L101" s="4"/>
     </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="n">
         <v>161</v>
       </c>
@@ -6734,7 +6803,7 @@
       </c>
       <c r="L102" s="4"/>
     </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="n">
         <v>162</v>
       </c>
@@ -6769,7 +6838,7 @@
       </c>
       <c r="L103" s="4"/>
     </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="4" t="n">
         <v>163</v>
       </c>
@@ -6878,7 +6947,7 @@
       </c>
       <c r="L106" s="4"/>
     </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="4" t="n">
         <v>166</v>
       </c>
@@ -6913,7 +6982,7 @@
       </c>
       <c r="L107" s="4"/>
     </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="n">
         <v>167</v>
       </c>
@@ -6985,7 +7054,7 @@
       </c>
       <c r="L109" s="4"/>
     </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="n">
         <v>169</v>
       </c>
@@ -7020,7 +7089,7 @@
       </c>
       <c r="L110" s="4"/>
     </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="n">
         <v>170</v>
       </c>
@@ -7055,7 +7124,7 @@
       </c>
       <c r="L111" s="4"/>
     </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="n">
         <v>171</v>
       </c>
@@ -7090,7 +7159,7 @@
       </c>
       <c r="L112" s="4"/>
     </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="n">
         <v>176</v>
       </c>
@@ -7162,7 +7231,7 @@
       </c>
       <c r="L114" s="4"/>
     </row>
-    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="4" t="n">
         <v>178</v>
       </c>
@@ -7197,7 +7266,7 @@
       </c>
       <c r="L115" s="4"/>
     </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="4" t="n">
         <v>179</v>
       </c>
@@ -7232,7 +7301,7 @@
       </c>
       <c r="L116" s="4"/>
     </row>
-    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="4" t="n">
         <v>180</v>
       </c>
@@ -7267,7 +7336,7 @@
       </c>
       <c r="L117" s="4"/>
     </row>
-    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="4" t="n">
         <v>181</v>
       </c>
@@ -7376,7 +7445,7 @@
       </c>
       <c r="L120" s="4"/>
     </row>
-    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="4" t="n">
         <v>185</v>
       </c>
@@ -7411,7 +7480,7 @@
       </c>
       <c r="L121" s="4"/>
     </row>
-    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="4" t="n">
         <v>186</v>
       </c>
@@ -7446,7 +7515,7 @@
       </c>
       <c r="L122" s="4"/>
     </row>
-    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="4" t="n">
         <v>187</v>
       </c>
@@ -7481,7 +7550,7 @@
       </c>
       <c r="L123" s="4"/>
     </row>
-    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="4" t="n">
         <v>188</v>
       </c>
@@ -7516,7 +7585,7 @@
       </c>
       <c r="L124" s="4"/>
     </row>
-    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="4" t="n">
         <v>191</v>
       </c>
@@ -7551,7 +7620,7 @@
       </c>
       <c r="L125" s="4"/>
     </row>
-    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="4" t="n">
         <v>192</v>
       </c>
@@ -7586,7 +7655,7 @@
       </c>
       <c r="L126" s="4"/>
     </row>
-    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="4" t="n">
         <v>193</v>
       </c>
@@ -7658,7 +7727,7 @@
       </c>
       <c r="L128" s="4"/>
     </row>
-    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="n">
         <v>195</v>
       </c>
@@ -7693,7 +7762,7 @@
       </c>
       <c r="L129" s="4"/>
     </row>
-    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="4" t="n">
         <v>196</v>
       </c>
@@ -7728,7 +7797,7 @@
       </c>
       <c r="L130" s="4"/>
     </row>
-    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="4" t="n">
         <v>197</v>
       </c>
@@ -7763,7 +7832,7 @@
       </c>
       <c r="L131" s="4"/>
     </row>
-    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="4" t="n">
         <v>198</v>
       </c>
@@ -7909,7 +7978,7 @@
       </c>
       <c r="L135" s="4"/>
     </row>
-    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="4" t="n">
         <v>206</v>
       </c>
@@ -7944,7 +8013,7 @@
       </c>
       <c r="L136" s="4"/>
     </row>
-    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="4" t="n">
         <v>208</v>
       </c>
@@ -8016,7 +8085,7 @@
       </c>
       <c r="L138" s="4"/>
     </row>
-    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="4" t="n">
         <v>213</v>
       </c>
@@ -8051,7 +8120,7 @@
       </c>
       <c r="L139" s="4"/>
     </row>
-    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="4" t="n">
         <v>214</v>
       </c>
@@ -8086,7 +8155,7 @@
       </c>
       <c r="L140" s="4"/>
     </row>
-    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="4" t="n">
         <v>215</v>
       </c>
@@ -8121,7 +8190,7 @@
       </c>
       <c r="L141" s="4"/>
     </row>
-    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="4" t="n">
         <v>216</v>
       </c>
@@ -8156,7 +8225,7 @@
       </c>
       <c r="L142" s="4"/>
     </row>
-    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="4" t="n">
         <v>220</v>
       </c>
@@ -8191,7 +8260,7 @@
       </c>
       <c r="L143" s="4"/>
     </row>
-    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="4" t="n">
         <v>221</v>
       </c>
@@ -8226,7 +8295,7 @@
       </c>
       <c r="L144" s="4"/>
     </row>
-    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="4" t="n">
         <v>222</v>
       </c>
@@ -8261,7 +8330,7 @@
       </c>
       <c r="L145" s="4"/>
     </row>
-    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="4" t="n">
         <v>223</v>
       </c>
@@ -8296,7 +8365,7 @@
       </c>
       <c r="L146" s="4"/>
     </row>
-    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="4" t="n">
         <v>224</v>
       </c>
@@ -8331,7 +8400,7 @@
       </c>
       <c r="L147" s="4"/>
     </row>
-    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="4" t="n">
         <v>227</v>
       </c>
@@ -8366,7 +8435,7 @@
       </c>
       <c r="L148" s="4"/>
     </row>
-    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="4" t="n">
         <v>228</v>
       </c>
@@ -8401,7 +8470,7 @@
       </c>
       <c r="L149" s="4"/>
     </row>
-    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="4" t="n">
         <v>229</v>
       </c>
@@ -8436,7 +8505,7 @@
       </c>
       <c r="L150" s="4"/>
     </row>
-    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="4" t="n">
         <v>230</v>
       </c>
@@ -8471,7 +8540,7 @@
       </c>
       <c r="L151" s="4"/>
     </row>
-    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="4" t="n">
         <v>231</v>
       </c>
@@ -8506,7 +8575,7 @@
       </c>
       <c r="L152" s="4"/>
     </row>
-    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="4" t="n">
         <v>232</v>
       </c>
@@ -8541,7 +8610,7 @@
       </c>
       <c r="L153" s="4"/>
     </row>
-    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="4" t="n">
         <v>234</v>
       </c>
@@ -8576,7 +8645,7 @@
       </c>
       <c r="L154" s="4"/>
     </row>
-    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="4" t="n">
         <v>235</v>
       </c>
@@ -8611,7 +8680,7 @@
       </c>
       <c r="L155" s="4"/>
     </row>
-    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="4" t="n">
         <v>238</v>
       </c>
@@ -8646,7 +8715,7 @@
       </c>
       <c r="L156" s="4"/>
     </row>
-    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="4" t="n">
         <v>240</v>
       </c>
@@ -8681,7 +8750,7 @@
       </c>
       <c r="L157" s="4"/>
     </row>
-    <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="4" t="n">
         <v>241</v>
       </c>
@@ -8716,7 +8785,7 @@
       </c>
       <c r="L158" s="4"/>
     </row>
-    <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="4" t="n">
         <v>242</v>
       </c>
@@ -8751,7 +8820,7 @@
       </c>
       <c r="L159" s="4"/>
     </row>
-    <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="4" t="n">
         <v>243</v>
       </c>
@@ -8786,7 +8855,7 @@
       </c>
       <c r="L160" s="4"/>
     </row>
-    <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="4" t="n">
         <v>244</v>
       </c>
@@ -8821,7 +8890,7 @@
       </c>
       <c r="L161" s="4"/>
     </row>
-    <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="4" t="n">
         <v>246</v>
       </c>
@@ -8856,7 +8925,7 @@
       </c>
       <c r="L162" s="4"/>
     </row>
-    <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="4" t="n">
         <v>248</v>
       </c>
@@ -8891,7 +8960,7 @@
       </c>
       <c r="L163" s="4"/>
     </row>
-    <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="4" t="n">
         <v>250</v>
       </c>
@@ -8926,7 +8995,7 @@
       </c>
       <c r="L164" s="4"/>
     </row>
-    <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="4" t="n">
         <v>251</v>
       </c>
@@ -9035,7 +9104,7 @@
       </c>
       <c r="L167" s="4"/>
     </row>
-    <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="4" t="n">
         <v>254</v>
       </c>
@@ -9070,7 +9139,7 @@
       </c>
       <c r="L168" s="4"/>
     </row>
-    <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="4" t="n">
         <v>255</v>
       </c>
@@ -9179,7 +9248,7 @@
       </c>
       <c r="L171" s="4"/>
     </row>
-    <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="4" t="n">
         <v>258</v>
       </c>
@@ -9214,7 +9283,7 @@
       </c>
       <c r="L172" s="4"/>
     </row>
-    <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="4" t="n">
         <v>259</v>
       </c>
@@ -9249,7 +9318,7 @@
       </c>
       <c r="L173" s="4"/>
     </row>
-    <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="4" t="n">
         <v>260</v>
       </c>
@@ -9284,7 +9353,7 @@
       </c>
       <c r="L174" s="4"/>
     </row>
-    <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="4" t="n">
         <v>261</v>
       </c>
@@ -9319,7 +9388,7 @@
       </c>
       <c r="L175" s="4"/>
     </row>
-    <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="4" t="n">
         <v>264</v>
       </c>
@@ -9354,7 +9423,7 @@
       </c>
       <c r="L176" s="4"/>
     </row>
-    <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="4" t="n">
         <v>265</v>
       </c>
@@ -9389,7 +9458,7 @@
       </c>
       <c r="L177" s="4"/>
     </row>
-    <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="4" t="n">
         <v>266</v>
       </c>
@@ -9424,7 +9493,7 @@
       </c>
       <c r="L178" s="4"/>
     </row>
-    <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="4" t="n">
         <v>267</v>
       </c>
@@ -9459,7 +9528,7 @@
       </c>
       <c r="L179" s="4"/>
     </row>
-    <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="4" t="n">
         <v>269</v>
       </c>
@@ -9494,7 +9563,7 @@
       </c>
       <c r="L180" s="4"/>
     </row>
-    <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="4" t="n">
         <v>273</v>
       </c>
@@ -9529,7 +9598,7 @@
       </c>
       <c r="L181" s="4"/>
     </row>
-    <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="4" t="n">
         <v>274</v>
       </c>
@@ -9564,7 +9633,7 @@
       </c>
       <c r="L182" s="4"/>
     </row>
-    <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="4" t="n">
         <v>276</v>
       </c>
@@ -9599,7 +9668,7 @@
       </c>
       <c r="L183" s="4"/>
     </row>
-    <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="4" t="n">
         <v>277</v>
       </c>
@@ -9634,7 +9703,7 @@
       </c>
       <c r="L184" s="4"/>
     </row>
-    <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="4" t="n">
         <v>278</v>
       </c>
@@ -9669,7 +9738,7 @@
       </c>
       <c r="L185" s="4"/>
     </row>
-    <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="4" t="n">
         <v>279</v>
       </c>
@@ -9704,7 +9773,7 @@
       </c>
       <c r="L186" s="4"/>
     </row>
-    <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="4" t="n">
         <v>280</v>
       </c>
@@ -9739,7 +9808,7 @@
       </c>
       <c r="L187" s="4"/>
     </row>
-    <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="4" t="n">
         <v>281</v>
       </c>
@@ -9774,7 +9843,7 @@
       </c>
       <c r="L188" s="4"/>
     </row>
-    <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="4" t="n">
         <v>282</v>
       </c>
@@ -9809,7 +9878,7 @@
       </c>
       <c r="L189" s="4"/>
     </row>
-    <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="4" t="n">
         <v>283</v>
       </c>
@@ -9844,7 +9913,7 @@
       </c>
       <c r="L190" s="4"/>
     </row>
-    <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="4" t="n">
         <v>284</v>
       </c>
@@ -9879,7 +9948,7 @@
       </c>
       <c r="L191" s="4"/>
     </row>
-    <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="4" t="n">
         <v>285</v>
       </c>
@@ -9914,7 +9983,7 @@
       </c>
       <c r="L192" s="4"/>
     </row>
-    <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="4" t="n">
         <v>286</v>
       </c>
@@ -9949,7 +10018,7 @@
       </c>
       <c r="L193" s="4"/>
     </row>
-    <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="4" t="n">
         <v>287</v>
       </c>
@@ -9984,7 +10053,7 @@
       </c>
       <c r="L194" s="4"/>
     </row>
-    <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="4" t="n">
         <v>288</v>
       </c>
@@ -10019,7 +10088,7 @@
       </c>
       <c r="L195" s="4"/>
     </row>
-    <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="4" t="n">
         <v>289</v>
       </c>
@@ -10054,7 +10123,7 @@
       </c>
       <c r="L196" s="4"/>
     </row>
-    <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="4" t="n">
         <v>291</v>
       </c>
@@ -10089,7 +10158,7 @@
       </c>
       <c r="L197" s="4"/>
     </row>
-    <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="4" t="n">
         <v>292</v>
       </c>
@@ -10124,7 +10193,7 @@
       </c>
       <c r="L198" s="4"/>
     </row>
-    <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="4" t="n">
         <v>293</v>
       </c>
@@ -10159,7 +10228,7 @@
       </c>
       <c r="L199" s="4"/>
     </row>
-    <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="4" t="n">
         <v>295</v>
       </c>
@@ -10194,7 +10263,7 @@
       </c>
       <c r="L200" s="4"/>
     </row>
-    <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="4" t="n">
         <v>296</v>
       </c>
@@ -10229,7 +10298,7 @@
       </c>
       <c r="L201" s="4"/>
     </row>
-    <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="4" t="n">
         <v>298</v>
       </c>
@@ -10264,7 +10333,7 @@
       </c>
       <c r="L202" s="4"/>
     </row>
-    <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="4" t="n">
         <v>299</v>
       </c>
@@ -10299,7 +10368,7 @@
       </c>
       <c r="L203" s="4"/>
     </row>
-    <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="4" t="n">
         <v>301</v>
       </c>
@@ -10334,7 +10403,7 @@
       </c>
       <c r="L204" s="4"/>
     </row>
-    <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="4" t="n">
         <v>302</v>
       </c>
@@ -10369,7 +10438,7 @@
       </c>
       <c r="L205" s="4"/>
     </row>
-    <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="4" t="n">
         <v>303</v>
       </c>
@@ -10404,7 +10473,7 @@
       </c>
       <c r="L206" s="4"/>
     </row>
-    <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="4" t="n">
         <v>305</v>
       </c>
@@ -10439,7 +10508,7 @@
       </c>
       <c r="L207" s="4"/>
     </row>
-    <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="4" t="n">
         <v>306</v>
       </c>
@@ -10474,7 +10543,7 @@
       </c>
       <c r="L208" s="4"/>
     </row>
-    <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="4" t="n">
         <v>309</v>
       </c>
@@ -10509,7 +10578,7 @@
       </c>
       <c r="L209" s="4"/>
     </row>
-    <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="4" t="n">
         <v>310</v>
       </c>
@@ -10544,7 +10613,7 @@
       </c>
       <c r="L210" s="4"/>
     </row>
-    <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="4" t="n">
         <v>311</v>
       </c>
@@ -10579,7 +10648,7 @@
       </c>
       <c r="L211" s="4"/>
     </row>
-    <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="4" t="n">
         <v>312</v>
       </c>
@@ -10688,7 +10757,7 @@
       </c>
       <c r="L214" s="4"/>
     </row>
-    <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="4" t="n">
         <v>315</v>
       </c>
@@ -10723,7 +10792,7 @@
       </c>
       <c r="L215" s="4"/>
     </row>
-    <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="4" t="n">
         <v>316</v>
       </c>
@@ -10758,7 +10827,7 @@
       </c>
       <c r="L216" s="4"/>
     </row>
-    <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="4" t="n">
         <v>317</v>
       </c>
@@ -10830,7 +10899,7 @@
       </c>
       <c r="L218" s="4"/>
     </row>
-    <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="4" t="n">
         <v>319</v>
       </c>
@@ -10865,7 +10934,7 @@
       </c>
       <c r="L219" s="4"/>
     </row>
-    <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="4" t="n">
         <v>320</v>
       </c>
@@ -10900,7 +10969,7 @@
       </c>
       <c r="L220" s="4"/>
     </row>
-    <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="4" t="n">
         <v>321</v>
       </c>
@@ -10935,7 +11004,7 @@
       </c>
       <c r="L221" s="4"/>
     </row>
-    <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="4" t="n">
         <v>322</v>
       </c>
@@ -10970,7 +11039,7 @@
       </c>
       <c r="L222" s="4"/>
     </row>
-    <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="4" t="n">
         <v>323</v>
       </c>
@@ -11005,7 +11074,7 @@
       </c>
       <c r="L223" s="4"/>
     </row>
-    <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="4" t="n">
         <v>324</v>
       </c>
@@ -11040,7 +11109,7 @@
       </c>
       <c r="L224" s="4"/>
     </row>
-    <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="4" t="n">
         <v>325</v>
       </c>
@@ -11075,7 +11144,7 @@
       </c>
       <c r="L225" s="4"/>
     </row>
-    <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="4" t="n">
         <v>326</v>
       </c>
@@ -11110,7 +11179,7 @@
       </c>
       <c r="L226" s="4"/>
     </row>
-    <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="4" t="n">
         <v>329</v>
       </c>
@@ -11145,7 +11214,7 @@
       </c>
       <c r="L227" s="4"/>
     </row>
-    <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="4" t="n">
         <v>330</v>
       </c>
@@ -11328,7 +11397,7 @@
       </c>
       <c r="L232" s="4"/>
     </row>
-    <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="4" t="n">
         <v>335</v>
       </c>
@@ -11363,7 +11432,7 @@
       </c>
       <c r="L233" s="4"/>
     </row>
-    <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="4" t="n">
         <v>336</v>
       </c>
@@ -11398,7 +11467,7 @@
       </c>
       <c r="L234" s="4"/>
     </row>
-    <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="4" t="n">
         <v>337</v>
       </c>
@@ -11468,7 +11537,7 @@
       </c>
       <c r="L236" s="4"/>
     </row>
-    <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="4" t="n">
         <v>339</v>
       </c>
@@ -11503,7 +11572,7 @@
       </c>
       <c r="L237" s="4"/>
     </row>
-    <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="4" t="n">
         <v>340</v>
       </c>
@@ -11612,7 +11681,7 @@
       </c>
       <c r="L240" s="4"/>
     </row>
-    <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="4" t="n">
         <v>346</v>
       </c>
@@ -11647,7 +11716,7 @@
       </c>
       <c r="L241" s="4"/>
     </row>
-    <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="4" t="n">
         <v>347</v>
       </c>
@@ -11682,7 +11751,7 @@
       </c>
       <c r="L242" s="4"/>
     </row>
-    <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="4" t="n">
         <v>349</v>
       </c>
@@ -11754,7 +11823,7 @@
       </c>
       <c r="L244" s="4"/>
     </row>
-    <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="4" t="n">
         <v>351</v>
       </c>
@@ -11789,7 +11858,7 @@
       </c>
       <c r="L245" s="4"/>
     </row>
-    <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="4" t="n">
         <v>352</v>
       </c>
@@ -11824,7 +11893,7 @@
       </c>
       <c r="L246" s="4"/>
     </row>
-    <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="4" t="n">
         <v>353</v>
       </c>
@@ -11859,7 +11928,7 @@
       </c>
       <c r="L247" s="4"/>
     </row>
-    <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="4" t="n">
         <v>354</v>
       </c>
@@ -11894,7 +11963,7 @@
       </c>
       <c r="L248" s="4"/>
     </row>
-    <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="8" t="n">
         <v>247</v>
       </c>
@@ -11930,7 +11999,7 @@
       </c>
       <c r="L249" s="8"/>
     </row>
-    <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="8" t="n">
         <v>248</v>
       </c>
@@ -11966,7 +12035,7 @@
       </c>
       <c r="L250" s="8"/>
     </row>
-    <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="8" t="n">
         <v>249</v>
       </c>
@@ -12002,7 +12071,7 @@
       </c>
       <c r="L251" s="8"/>
     </row>
-    <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="8" t="n">
         <v>250</v>
       </c>
@@ -12038,8 +12107,266 @@
       </c>
       <c r="L252" s="8"/>
     </row>
+    <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="8" t="n">
+        <v>251</v>
+      </c>
+      <c r="B253" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C253" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="D253" s="10" t="s">
+        <v>797</v>
+      </c>
+      <c r="E253" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F253" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="G253" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="H253" s="8" t="s">
+        <v>799</v>
+      </c>
+      <c r="I253" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J253" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K253" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L253" s="8"/>
+    </row>
+    <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="8" t="n">
+        <v>252</v>
+      </c>
+      <c r="B254" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C254" s="10" t="s">
+        <v>800</v>
+      </c>
+      <c r="D254" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="E254" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F254" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="G254" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="H254" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="I254" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J254" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K254" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L254" s="8"/>
+    </row>
+    <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="8" t="n">
+        <v>253</v>
+      </c>
+      <c r="B255" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C255" s="10" t="s">
+        <v>803</v>
+      </c>
+      <c r="D255" s="10" t="s">
+        <v>804</v>
+      </c>
+      <c r="E255" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F255" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G255" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="H255" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="I255" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J255" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K255" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L255" s="8"/>
+    </row>
+    <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="8" t="n">
+        <v>254</v>
+      </c>
+      <c r="B256" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C256" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="D256" s="10" t="s">
+        <v>807</v>
+      </c>
+      <c r="E256" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F256" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G256" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H256" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="I256" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J256" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K256" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L256" s="8"/>
+    </row>
+    <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="8" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C257" s="10" t="s">
+        <v>809</v>
+      </c>
+      <c r="D257" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="E257" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F257" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="G257" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="H257" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="I257" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J257" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K257" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L257" s="8"/>
+    </row>
+    <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="8" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C258" s="10" t="s">
+        <v>812</v>
+      </c>
+      <c r="D258" s="10" t="s">
+        <v>813</v>
+      </c>
+      <c r="E258" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F258" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G258" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="H258" s="8" t="s">
+        <v>814</v>
+      </c>
+      <c r="I258" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J258" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K258" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L258" s="8"/>
+    </row>
+    <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="8" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C259" s="10" t="s">
+        <v>815</v>
+      </c>
+      <c r="D259" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="E259" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F259" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G259" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H259" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="I259" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J259" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K259" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L259" s="8"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:L248"/>
+  <autoFilter ref="A2:L259">
+    <filterColumn colId="9">
+      <customFilters and="true">
+        <customFilter operator="**none**" val=""/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
@@ -12308,6 +12635,13 @@
     <hyperlink ref="B250" r:id="rId248" display="▶ Play"/>
     <hyperlink ref="B251" r:id="rId249" display="▶ Play"/>
     <hyperlink ref="B252" r:id="rId250" display="▶ Play"/>
+    <hyperlink ref="B253" r:id="rId251" display="▶ Play"/>
+    <hyperlink ref="B254" r:id="rId252" display="▶ Play"/>
+    <hyperlink ref="B255" r:id="rId253" display="▶ Play"/>
+    <hyperlink ref="B256" r:id="rId254" display="▶ Play"/>
+    <hyperlink ref="B257" r:id="rId255" display="▶ Play"/>
+    <hyperlink ref="B258" r:id="rId256" display="▶ Play"/>
+    <hyperlink ref="B259" r:id="rId257" display="▶ Play"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12316,7 +12650,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId251"/>
+  <drawing r:id="rId258"/>
 </worksheet>
 </file>
 
@@ -12335,90 +12669,90 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>796</v>
+        <v>818</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>797</v>
+        <v>819</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>798</v>
+        <v>820</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>799</v>
+        <v>821</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>800</v>
+        <v>822</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>801</v>
+        <v>823</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>802</v>
+        <v>824</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>803</v>
+        <v>825</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>804</v>
+        <v>826</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>805</v>
+        <v>827</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>806</v>
+        <v>828</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>807</v>
+        <v>829</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>808</v>
+        <v>830</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>809</v>
+        <v>831</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>810</v>
+        <v>832</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>811</v>
+        <v>833</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>812</v>
+        <v>834</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>32</v>
+        <v>835</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>813</v>
+        <v>836</v>
       </c>
     </row>
   </sheetData>
@@ -12448,24 +12782,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>814</v>
+        <v>837</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>815</v>
+        <v>838</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>816</v>
+        <v>839</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>817</v>
+        <v>840</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>818</v>
+        <v>841</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>819</v>
+        <v>842</v>
       </c>
       <c r="B2" s="6" t="n">
         <v>0</v>
@@ -12474,13 +12808,13 @@
         <v>6</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>820</v>
+        <v>843</v>
       </c>
       <c r="E2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>821</v>
+        <v>844</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>6</v>
@@ -12489,15 +12823,15 @@
         <v>10</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>822</v>
+        <v>845</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>823</v>
+        <v>846</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>824</v>
+        <v>847</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>10</v>
@@ -12506,7 +12840,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>825</v>
+        <v>848</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>791</v>
@@ -12514,7 +12848,7 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>826</v>
+        <v>849</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>14</v>
@@ -12523,15 +12857,15 @@
         <v>17</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>827</v>
+        <v>850</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>823</v>
+        <v>846</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>828</v>
+        <v>851</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>17</v>
@@ -12540,13 +12874,13 @@
         <v>20</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>829</v>
+        <v>852</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>830</v>
+        <v>853</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>20</v>
@@ -12555,10 +12889,10 @@
         <v>24</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>831</v>
+        <v>854</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>823</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -12590,10 +12924,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>832</v>
+        <v>855</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>833</v>
+        <v>856</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12605,7 +12939,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12617,7 +12951,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12641,7 +12975,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12653,7 +12987,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12665,7 +12999,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12689,7 +13023,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12761,7 +13095,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12785,7 +13119,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12797,7 +13131,7 @@
         <v>13</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12821,7 +13155,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12833,7 +13167,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12845,7 +13179,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12869,7 +13203,7 @@
         <v>15</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12881,7 +13215,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12917,7 +13251,7 @@
         <v>6</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12941,7 +13275,7 @@
         <v>8</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>834</v>
+        <v>857</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Refined_Radio_Control.xlsx
+++ b/Refined_Radio_Control.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Genres" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Song Library'!$A$2:$L$259</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Song Library'!$A$2:$L$248</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="835">
   <si>
     <t xml:space="preserve">REFINED RADIO — MASTER CONTROL SHEET</t>
   </si>
@@ -2417,72 +2417,6 @@
     <t xml:space="preserve">Awoken the Master</t>
   </si>
   <si>
-    <t xml:space="preserve">music/Sweet Release (Chill).mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweet Release (Chill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweet Release</t>
-  </si>
-  <si>
-    <t xml:space="preserve">music/He Strengthens Me (Alternative 2000s Rock).mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">He Strengthens Me (Alt Rock)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">He Strengthens Me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">music/Shine His Light (K -Pop).mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shine His Light (K-Pop)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shine His Light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">music/I Can Count on You (Country).mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Can Count on You (Country)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Can Count on You</t>
-  </si>
-  <si>
-    <t xml:space="preserve">music/What Must I Do (2000s Alternative Metal).mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What Must I Do (Alt Rock)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What Must I Do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">music/One Promise (R&amp;B).mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One Promise (R&amp;B)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One Promise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">music/Boots-A-Stompin’ (For the King) (Country).mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boots-A-Stompin’ (For the King) (Country)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boots-A-Stompin’</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rule</t>
   </si>
   <si>
@@ -2504,7 +2438,7 @@
     <t xml:space="preserve">Play-all rotation</t>
   </si>
   <si>
-    <t xml:space="preserve">Every song is always eligible; the whole catalog cycles before anything repeats.</t>
+    <t xml:space="preserve">Whole catalog plays before repeats.</t>
   </si>
   <si>
     <t xml:space="preserve">No immediate repeat</t>
@@ -2534,10 +2468,7 @@
     <t xml:space="preserve">Follow daypart clock</t>
   </si>
   <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OFF — full play-all: every song airs at any hour (dayparts no longer gate the music).</t>
+    <t xml:space="preserve">Covered genres play in their dayparts.</t>
   </si>
   <si>
     <t xml:space="preserve">Daypart Name</t>
@@ -3201,10 +3132,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="true">
+  <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L259"/>
+  <dimension ref="A1:L252"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3275,7 +3206,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="n">
         <v>1</v>
       </c>
@@ -3310,7 +3241,7 @@
       </c>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
@@ -3345,7 +3276,7 @@
       </c>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="n">
         <v>3</v>
       </c>
@@ -3380,7 +3311,7 @@
       </c>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="n">
         <v>4</v>
       </c>
@@ -3415,7 +3346,7 @@
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="n">
         <v>5</v>
       </c>
@@ -3524,7 +3455,7 @@
       </c>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="n">
         <v>8</v>
       </c>
@@ -3559,7 +3490,7 @@
       </c>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="n">
         <v>9</v>
       </c>
@@ -3594,7 +3525,7 @@
       </c>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="n">
         <v>10</v>
       </c>
@@ -3629,7 +3560,7 @@
       </c>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="n">
         <v>11</v>
       </c>
@@ -3664,7 +3595,7 @@
       </c>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
@@ -3736,7 +3667,7 @@
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="n">
         <v>17</v>
       </c>
@@ -3808,7 +3739,7 @@
       </c>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="n">
         <v>22</v>
       </c>
@@ -3843,7 +3774,7 @@
       </c>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="n">
         <v>23</v>
       </c>
@@ -3878,7 +3809,7 @@
       </c>
       <c r="L19" s="4"/>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="n">
         <v>25</v>
       </c>
@@ -3950,7 +3881,7 @@
       </c>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="n">
         <v>27</v>
       </c>
@@ -3985,7 +3916,7 @@
       </c>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="n">
         <v>29</v>
       </c>
@@ -4020,7 +3951,7 @@
       </c>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="n">
         <v>30</v>
       </c>
@@ -4055,7 +3986,7 @@
       </c>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="n">
         <v>32</v>
       </c>
@@ -4090,7 +4021,7 @@
       </c>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="n">
         <v>36</v>
       </c>
@@ -4125,7 +4056,7 @@
       </c>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="n">
         <v>38</v>
       </c>
@@ -4160,7 +4091,7 @@
       </c>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="n">
         <v>40</v>
       </c>
@@ -4195,7 +4126,7 @@
       </c>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="n">
         <v>42</v>
       </c>
@@ -4267,7 +4198,7 @@
       </c>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
         <v>44</v>
       </c>
@@ -4302,7 +4233,7 @@
       </c>
       <c r="L31" s="4"/>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="n">
         <v>45</v>
       </c>
@@ -4337,7 +4268,7 @@
       </c>
       <c r="L32" s="4"/>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="n">
         <v>46</v>
       </c>
@@ -4372,7 +4303,7 @@
       </c>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="n">
         <v>47</v>
       </c>
@@ -4407,7 +4338,7 @@
       </c>
       <c r="L34" s="4"/>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="n">
         <v>48</v>
       </c>
@@ -4442,7 +4373,7 @@
       </c>
       <c r="L35" s="4"/>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="n">
         <v>50</v>
       </c>
@@ -4477,7 +4408,7 @@
       </c>
       <c r="L36" s="4"/>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="n">
         <v>51</v>
       </c>
@@ -4512,7 +4443,7 @@
       </c>
       <c r="L37" s="4"/>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="n">
         <v>52</v>
       </c>
@@ -4547,7 +4478,7 @@
       </c>
       <c r="L38" s="4"/>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="n">
         <v>54</v>
       </c>
@@ -4582,7 +4513,7 @@
       </c>
       <c r="L39" s="4"/>
     </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="n">
         <v>56</v>
       </c>
@@ -4617,7 +4548,7 @@
       </c>
       <c r="L40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="n">
         <v>60</v>
       </c>
@@ -4652,7 +4583,7 @@
       </c>
       <c r="L41" s="4"/>
     </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="n">
         <v>61</v>
       </c>
@@ -4761,7 +4692,7 @@
       </c>
       <c r="L44" s="4"/>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="n">
         <v>65</v>
       </c>
@@ -4796,7 +4727,7 @@
       </c>
       <c r="L45" s="4"/>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="n">
         <v>66</v>
       </c>
@@ -4831,7 +4762,7 @@
       </c>
       <c r="L46" s="4"/>
     </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="n">
         <v>67</v>
       </c>
@@ -4866,7 +4797,7 @@
       </c>
       <c r="L47" s="4"/>
     </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="n">
         <v>68</v>
       </c>
@@ -4901,7 +4832,7 @@
       </c>
       <c r="L48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="n">
         <v>69</v>
       </c>
@@ -4936,7 +4867,7 @@
       </c>
       <c r="L49" s="4"/>
     </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="n">
         <v>70</v>
       </c>
@@ -4971,7 +4902,7 @@
       </c>
       <c r="L50" s="4"/>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="n">
         <v>73</v>
       </c>
@@ -5006,7 +4937,7 @@
       </c>
       <c r="L51" s="4"/>
     </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="n">
         <v>74</v>
       </c>
@@ -5041,7 +4972,7 @@
       </c>
       <c r="L52" s="4"/>
     </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="n">
         <v>77</v>
       </c>
@@ -5076,7 +5007,7 @@
       </c>
       <c r="L53" s="4"/>
     </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="n">
         <v>78</v>
       </c>
@@ -5111,7 +5042,7 @@
       </c>
       <c r="L54" s="4"/>
     </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="n">
         <v>79</v>
       </c>
@@ -5146,7 +5077,7 @@
       </c>
       <c r="L55" s="4"/>
     </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="n">
         <v>81</v>
       </c>
@@ -5181,7 +5112,7 @@
       </c>
       <c r="L56" s="4"/>
     </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="n">
         <v>84</v>
       </c>
@@ -5216,7 +5147,7 @@
       </c>
       <c r="L57" s="4"/>
     </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="n">
         <v>85</v>
       </c>
@@ -5251,7 +5182,7 @@
       </c>
       <c r="L58" s="4"/>
     </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="n">
         <v>86</v>
       </c>
@@ -5286,7 +5217,7 @@
       </c>
       <c r="L59" s="4"/>
     </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="n">
         <v>89</v>
       </c>
@@ -5321,7 +5252,7 @@
       </c>
       <c r="L60" s="4"/>
     </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="n">
         <v>91</v>
       </c>
@@ -5356,7 +5287,7 @@
       </c>
       <c r="L61" s="4"/>
     </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="n">
         <v>92</v>
       </c>
@@ -5428,7 +5359,7 @@
       </c>
       <c r="L63" s="4"/>
     </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="n">
         <v>96</v>
       </c>
@@ -5463,7 +5394,7 @@
       </c>
       <c r="L64" s="4"/>
     </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="n">
         <v>98</v>
       </c>
@@ -5498,7 +5429,7 @@
       </c>
       <c r="L65" s="4"/>
     </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="n">
         <v>102</v>
       </c>
@@ -5533,7 +5464,7 @@
       </c>
       <c r="L66" s="4"/>
     </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="n">
         <v>103</v>
       </c>
@@ -5605,7 +5536,7 @@
       </c>
       <c r="L68" s="4"/>
     </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="n">
         <v>105</v>
       </c>
@@ -5640,7 +5571,7 @@
       </c>
       <c r="L69" s="4"/>
     </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="n">
         <v>107</v>
       </c>
@@ -5675,7 +5606,7 @@
       </c>
       <c r="L70" s="4"/>
     </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="n">
         <v>108</v>
       </c>
@@ -5710,7 +5641,7 @@
       </c>
       <c r="L71" s="4"/>
     </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="n">
         <v>109</v>
       </c>
@@ -5745,7 +5676,7 @@
       </c>
       <c r="L72" s="4"/>
     </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="n">
         <v>111</v>
       </c>
@@ -5780,7 +5711,7 @@
       </c>
       <c r="L73" s="4"/>
     </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="n">
         <v>113</v>
       </c>
@@ -5815,7 +5746,7 @@
       </c>
       <c r="L74" s="4"/>
     </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="n">
         <v>114</v>
       </c>
@@ -5850,7 +5781,7 @@
       </c>
       <c r="L75" s="4"/>
     </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="n">
         <v>116</v>
       </c>
@@ -5885,7 +5816,7 @@
       </c>
       <c r="L76" s="4"/>
     </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="n">
         <v>118</v>
       </c>
@@ -5920,7 +5851,7 @@
       </c>
       <c r="L77" s="4"/>
     </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="n">
         <v>119</v>
       </c>
@@ -5955,7 +5886,7 @@
       </c>
       <c r="L78" s="4"/>
     </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="n">
         <v>124</v>
       </c>
@@ -5990,7 +5921,7 @@
       </c>
       <c r="L79" s="4"/>
     </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="n">
         <v>125</v>
       </c>
@@ -6025,7 +5956,7 @@
       </c>
       <c r="L80" s="4"/>
     </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="n">
         <v>126</v>
       </c>
@@ -6060,7 +5991,7 @@
       </c>
       <c r="L81" s="4"/>
     </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="n">
         <v>131</v>
       </c>
@@ -6095,7 +6026,7 @@
       </c>
       <c r="L82" s="4"/>
     </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="n">
         <v>132</v>
       </c>
@@ -6130,7 +6061,7 @@
       </c>
       <c r="L83" s="4"/>
     </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="n">
         <v>135</v>
       </c>
@@ -6165,7 +6096,7 @@
       </c>
       <c r="L84" s="4"/>
     </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="n">
         <v>136</v>
       </c>
@@ -6200,7 +6131,7 @@
       </c>
       <c r="L85" s="4"/>
     </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="n">
         <v>137</v>
       </c>
@@ -6235,7 +6166,7 @@
       </c>
       <c r="L86" s="4"/>
     </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="n">
         <v>138</v>
       </c>
@@ -6270,7 +6201,7 @@
       </c>
       <c r="L87" s="4"/>
     </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="n">
         <v>139</v>
       </c>
@@ -6305,7 +6236,7 @@
       </c>
       <c r="L88" s="4"/>
     </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="n">
         <v>140</v>
       </c>
@@ -6377,7 +6308,7 @@
       </c>
       <c r="L90" s="4"/>
     </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="n">
         <v>145</v>
       </c>
@@ -6412,7 +6343,7 @@
       </c>
       <c r="L91" s="4"/>
     </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="n">
         <v>146</v>
       </c>
@@ -6484,7 +6415,7 @@
       </c>
       <c r="L93" s="4"/>
     </row>
-    <row r="94" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="n">
         <v>148</v>
       </c>
@@ -6519,7 +6450,7 @@
       </c>
       <c r="L94" s="4"/>
     </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="n">
         <v>149</v>
       </c>
@@ -6554,7 +6485,7 @@
       </c>
       <c r="L95" s="4"/>
     </row>
-    <row r="96" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="n">
         <v>152</v>
       </c>
@@ -6589,7 +6520,7 @@
       </c>
       <c r="L96" s="4"/>
     </row>
-    <row r="97" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="n">
         <v>153</v>
       </c>
@@ -6698,7 +6629,7 @@
       </c>
       <c r="L99" s="4"/>
     </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="n">
         <v>158</v>
       </c>
@@ -6733,7 +6664,7 @@
       </c>
       <c r="L100" s="4"/>
     </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="n">
         <v>160</v>
       </c>
@@ -6768,7 +6699,7 @@
       </c>
       <c r="L101" s="4"/>
     </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="n">
         <v>161</v>
       </c>
@@ -6803,7 +6734,7 @@
       </c>
       <c r="L102" s="4"/>
     </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="n">
         <v>162</v>
       </c>
@@ -6838,7 +6769,7 @@
       </c>
       <c r="L103" s="4"/>
     </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="4" t="n">
         <v>163</v>
       </c>
@@ -6947,7 +6878,7 @@
       </c>
       <c r="L106" s="4"/>
     </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="4" t="n">
         <v>166</v>
       </c>
@@ -6982,7 +6913,7 @@
       </c>
       <c r="L107" s="4"/>
     </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="n">
         <v>167</v>
       </c>
@@ -7054,7 +6985,7 @@
       </c>
       <c r="L109" s="4"/>
     </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="n">
         <v>169</v>
       </c>
@@ -7089,7 +7020,7 @@
       </c>
       <c r="L110" s="4"/>
     </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="n">
         <v>170</v>
       </c>
@@ -7124,7 +7055,7 @@
       </c>
       <c r="L111" s="4"/>
     </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="n">
         <v>171</v>
       </c>
@@ -7159,7 +7090,7 @@
       </c>
       <c r="L112" s="4"/>
     </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="n">
         <v>176</v>
       </c>
@@ -7231,7 +7162,7 @@
       </c>
       <c r="L114" s="4"/>
     </row>
-    <row r="115" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="4" t="n">
         <v>178</v>
       </c>
@@ -7266,7 +7197,7 @@
       </c>
       <c r="L115" s="4"/>
     </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="4" t="n">
         <v>179</v>
       </c>
@@ -7301,7 +7232,7 @@
       </c>
       <c r="L116" s="4"/>
     </row>
-    <row r="117" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="4" t="n">
         <v>180</v>
       </c>
@@ -7336,7 +7267,7 @@
       </c>
       <c r="L117" s="4"/>
     </row>
-    <row r="118" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="4" t="n">
         <v>181</v>
       </c>
@@ -7445,7 +7376,7 @@
       </c>
       <c r="L120" s="4"/>
     </row>
-    <row r="121" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="4" t="n">
         <v>185</v>
       </c>
@@ -7480,7 +7411,7 @@
       </c>
       <c r="L121" s="4"/>
     </row>
-    <row r="122" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="4" t="n">
         <v>186</v>
       </c>
@@ -7515,7 +7446,7 @@
       </c>
       <c r="L122" s="4"/>
     </row>
-    <row r="123" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="4" t="n">
         <v>187</v>
       </c>
@@ -7550,7 +7481,7 @@
       </c>
       <c r="L123" s="4"/>
     </row>
-    <row r="124" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="4" t="n">
         <v>188</v>
       </c>
@@ -7585,7 +7516,7 @@
       </c>
       <c r="L124" s="4"/>
     </row>
-    <row r="125" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="4" t="n">
         <v>191</v>
       </c>
@@ -7620,7 +7551,7 @@
       </c>
       <c r="L125" s="4"/>
     </row>
-    <row r="126" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="4" t="n">
         <v>192</v>
       </c>
@@ -7655,7 +7586,7 @@
       </c>
       <c r="L126" s="4"/>
     </row>
-    <row r="127" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="4" t="n">
         <v>193</v>
       </c>
@@ -7727,7 +7658,7 @@
       </c>
       <c r="L128" s="4"/>
     </row>
-    <row r="129" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="n">
         <v>195</v>
       </c>
@@ -7762,7 +7693,7 @@
       </c>
       <c r="L129" s="4"/>
     </row>
-    <row r="130" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="4" t="n">
         <v>196</v>
       </c>
@@ -7797,7 +7728,7 @@
       </c>
       <c r="L130" s="4"/>
     </row>
-    <row r="131" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="4" t="n">
         <v>197</v>
       </c>
@@ -7832,7 +7763,7 @@
       </c>
       <c r="L131" s="4"/>
     </row>
-    <row r="132" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="4" t="n">
         <v>198</v>
       </c>
@@ -7978,7 +7909,7 @@
       </c>
       <c r="L135" s="4"/>
     </row>
-    <row r="136" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="4" t="n">
         <v>206</v>
       </c>
@@ -8013,7 +7944,7 @@
       </c>
       <c r="L136" s="4"/>
     </row>
-    <row r="137" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="4" t="n">
         <v>208</v>
       </c>
@@ -8085,7 +8016,7 @@
       </c>
       <c r="L138" s="4"/>
     </row>
-    <row r="139" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="4" t="n">
         <v>213</v>
       </c>
@@ -8120,7 +8051,7 @@
       </c>
       <c r="L139" s="4"/>
     </row>
-    <row r="140" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="4" t="n">
         <v>214</v>
       </c>
@@ -8155,7 +8086,7 @@
       </c>
       <c r="L140" s="4"/>
     </row>
-    <row r="141" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="4" t="n">
         <v>215</v>
       </c>
@@ -8190,7 +8121,7 @@
       </c>
       <c r="L141" s="4"/>
     </row>
-    <row r="142" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="4" t="n">
         <v>216</v>
       </c>
@@ -8225,7 +8156,7 @@
       </c>
       <c r="L142" s="4"/>
     </row>
-    <row r="143" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="4" t="n">
         <v>220</v>
       </c>
@@ -8260,7 +8191,7 @@
       </c>
       <c r="L143" s="4"/>
     </row>
-    <row r="144" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="4" t="n">
         <v>221</v>
       </c>
@@ -8295,7 +8226,7 @@
       </c>
       <c r="L144" s="4"/>
     </row>
-    <row r="145" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="4" t="n">
         <v>222</v>
       </c>
@@ -8330,7 +8261,7 @@
       </c>
       <c r="L145" s="4"/>
     </row>
-    <row r="146" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="4" t="n">
         <v>223</v>
       </c>
@@ -8365,7 +8296,7 @@
       </c>
       <c r="L146" s="4"/>
     </row>
-    <row r="147" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="4" t="n">
         <v>224</v>
       </c>
@@ -8400,7 +8331,7 @@
       </c>
       <c r="L147" s="4"/>
     </row>
-    <row r="148" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="4" t="n">
         <v>227</v>
       </c>
@@ -8435,7 +8366,7 @@
       </c>
       <c r="L148" s="4"/>
     </row>
-    <row r="149" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="4" t="n">
         <v>228</v>
       </c>
@@ -8470,7 +8401,7 @@
       </c>
       <c r="L149" s="4"/>
     </row>
-    <row r="150" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="4" t="n">
         <v>229</v>
       </c>
@@ -8505,7 +8436,7 @@
       </c>
       <c r="L150" s="4"/>
     </row>
-    <row r="151" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="4" t="n">
         <v>230</v>
       </c>
@@ -8540,7 +8471,7 @@
       </c>
       <c r="L151" s="4"/>
     </row>
-    <row r="152" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="4" t="n">
         <v>231</v>
       </c>
@@ -8575,7 +8506,7 @@
       </c>
       <c r="L152" s="4"/>
     </row>
-    <row r="153" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="4" t="n">
         <v>232</v>
       </c>
@@ -8610,7 +8541,7 @@
       </c>
       <c r="L153" s="4"/>
     </row>
-    <row r="154" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="4" t="n">
         <v>234</v>
       </c>
@@ -8645,7 +8576,7 @@
       </c>
       <c r="L154" s="4"/>
     </row>
-    <row r="155" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="4" t="n">
         <v>235</v>
       </c>
@@ -8680,7 +8611,7 @@
       </c>
       <c r="L155" s="4"/>
     </row>
-    <row r="156" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="4" t="n">
         <v>238</v>
       </c>
@@ -8715,7 +8646,7 @@
       </c>
       <c r="L156" s="4"/>
     </row>
-    <row r="157" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="4" t="n">
         <v>240</v>
       </c>
@@ -8750,7 +8681,7 @@
       </c>
       <c r="L157" s="4"/>
     </row>
-    <row r="158" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="4" t="n">
         <v>241</v>
       </c>
@@ -8785,7 +8716,7 @@
       </c>
       <c r="L158" s="4"/>
     </row>
-    <row r="159" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="4" t="n">
         <v>242</v>
       </c>
@@ -8820,7 +8751,7 @@
       </c>
       <c r="L159" s="4"/>
     </row>
-    <row r="160" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="4" t="n">
         <v>243</v>
       </c>
@@ -8855,7 +8786,7 @@
       </c>
       <c r="L160" s="4"/>
     </row>
-    <row r="161" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="4" t="n">
         <v>244</v>
       </c>
@@ -8890,7 +8821,7 @@
       </c>
       <c r="L161" s="4"/>
     </row>
-    <row r="162" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="4" t="n">
         <v>246</v>
       </c>
@@ -8925,7 +8856,7 @@
       </c>
       <c r="L162" s="4"/>
     </row>
-    <row r="163" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="4" t="n">
         <v>248</v>
       </c>
@@ -8960,7 +8891,7 @@
       </c>
       <c r="L163" s="4"/>
     </row>
-    <row r="164" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="4" t="n">
         <v>250</v>
       </c>
@@ -8995,7 +8926,7 @@
       </c>
       <c r="L164" s="4"/>
     </row>
-    <row r="165" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="4" t="n">
         <v>251</v>
       </c>
@@ -9104,7 +9035,7 @@
       </c>
       <c r="L167" s="4"/>
     </row>
-    <row r="168" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="4" t="n">
         <v>254</v>
       </c>
@@ -9139,7 +9070,7 @@
       </c>
       <c r="L168" s="4"/>
     </row>
-    <row r="169" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="4" t="n">
         <v>255</v>
       </c>
@@ -9248,7 +9179,7 @@
       </c>
       <c r="L171" s="4"/>
     </row>
-    <row r="172" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="4" t="n">
         <v>258</v>
       </c>
@@ -9283,7 +9214,7 @@
       </c>
       <c r="L172" s="4"/>
     </row>
-    <row r="173" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="4" t="n">
         <v>259</v>
       </c>
@@ -9318,7 +9249,7 @@
       </c>
       <c r="L173" s="4"/>
     </row>
-    <row r="174" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="4" t="n">
         <v>260</v>
       </c>
@@ -9353,7 +9284,7 @@
       </c>
       <c r="L174" s="4"/>
     </row>
-    <row r="175" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="4" t="n">
         <v>261</v>
       </c>
@@ -9388,7 +9319,7 @@
       </c>
       <c r="L175" s="4"/>
     </row>
-    <row r="176" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="4" t="n">
         <v>264</v>
       </c>
@@ -9423,7 +9354,7 @@
       </c>
       <c r="L176" s="4"/>
     </row>
-    <row r="177" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="4" t="n">
         <v>265</v>
       </c>
@@ -9458,7 +9389,7 @@
       </c>
       <c r="L177" s="4"/>
     </row>
-    <row r="178" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="4" t="n">
         <v>266</v>
       </c>
@@ -9493,7 +9424,7 @@
       </c>
       <c r="L178" s="4"/>
     </row>
-    <row r="179" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="4" t="n">
         <v>267</v>
       </c>
@@ -9528,7 +9459,7 @@
       </c>
       <c r="L179" s="4"/>
     </row>
-    <row r="180" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="4" t="n">
         <v>269</v>
       </c>
@@ -9563,7 +9494,7 @@
       </c>
       <c r="L180" s="4"/>
     </row>
-    <row r="181" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="4" t="n">
         <v>273</v>
       </c>
@@ -9598,7 +9529,7 @@
       </c>
       <c r="L181" s="4"/>
     </row>
-    <row r="182" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="4" t="n">
         <v>274</v>
       </c>
@@ -9633,7 +9564,7 @@
       </c>
       <c r="L182" s="4"/>
     </row>
-    <row r="183" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="4" t="n">
         <v>276</v>
       </c>
@@ -9668,7 +9599,7 @@
       </c>
       <c r="L183" s="4"/>
     </row>
-    <row r="184" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="4" t="n">
         <v>277</v>
       </c>
@@ -9703,7 +9634,7 @@
       </c>
       <c r="L184" s="4"/>
     </row>
-    <row r="185" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="4" t="n">
         <v>278</v>
       </c>
@@ -9738,7 +9669,7 @@
       </c>
       <c r="L185" s="4"/>
     </row>
-    <row r="186" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="4" t="n">
         <v>279</v>
       </c>
@@ -9773,7 +9704,7 @@
       </c>
       <c r="L186" s="4"/>
     </row>
-    <row r="187" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="4" t="n">
         <v>280</v>
       </c>
@@ -9808,7 +9739,7 @@
       </c>
       <c r="L187" s="4"/>
     </row>
-    <row r="188" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="4" t="n">
         <v>281</v>
       </c>
@@ -9843,7 +9774,7 @@
       </c>
       <c r="L188" s="4"/>
     </row>
-    <row r="189" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="4" t="n">
         <v>282</v>
       </c>
@@ -9878,7 +9809,7 @@
       </c>
       <c r="L189" s="4"/>
     </row>
-    <row r="190" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="4" t="n">
         <v>283</v>
       </c>
@@ -9913,7 +9844,7 @@
       </c>
       <c r="L190" s="4"/>
     </row>
-    <row r="191" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="4" t="n">
         <v>284</v>
       </c>
@@ -9948,7 +9879,7 @@
       </c>
       <c r="L191" s="4"/>
     </row>
-    <row r="192" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="4" t="n">
         <v>285</v>
       </c>
@@ -9983,7 +9914,7 @@
       </c>
       <c r="L192" s="4"/>
     </row>
-    <row r="193" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="4" t="n">
         <v>286</v>
       </c>
@@ -10018,7 +9949,7 @@
       </c>
       <c r="L193" s="4"/>
     </row>
-    <row r="194" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="4" t="n">
         <v>287</v>
       </c>
@@ -10053,7 +9984,7 @@
       </c>
       <c r="L194" s="4"/>
     </row>
-    <row r="195" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="4" t="n">
         <v>288</v>
       </c>
@@ -10088,7 +10019,7 @@
       </c>
       <c r="L195" s="4"/>
     </row>
-    <row r="196" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="4" t="n">
         <v>289</v>
       </c>
@@ -10123,7 +10054,7 @@
       </c>
       <c r="L196" s="4"/>
     </row>
-    <row r="197" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="4" t="n">
         <v>291</v>
       </c>
@@ -10158,7 +10089,7 @@
       </c>
       <c r="L197" s="4"/>
     </row>
-    <row r="198" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="4" t="n">
         <v>292</v>
       </c>
@@ -10193,7 +10124,7 @@
       </c>
       <c r="L198" s="4"/>
     </row>
-    <row r="199" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="4" t="n">
         <v>293</v>
       </c>
@@ -10228,7 +10159,7 @@
       </c>
       <c r="L199" s="4"/>
     </row>
-    <row r="200" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="4" t="n">
         <v>295</v>
       </c>
@@ -10263,7 +10194,7 @@
       </c>
       <c r="L200" s="4"/>
     </row>
-    <row r="201" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="4" t="n">
         <v>296</v>
       </c>
@@ -10298,7 +10229,7 @@
       </c>
       <c r="L201" s="4"/>
     </row>
-    <row r="202" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="4" t="n">
         <v>298</v>
       </c>
@@ -10333,7 +10264,7 @@
       </c>
       <c r="L202" s="4"/>
     </row>
-    <row r="203" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="4" t="n">
         <v>299</v>
       </c>
@@ -10368,7 +10299,7 @@
       </c>
       <c r="L203" s="4"/>
     </row>
-    <row r="204" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="4" t="n">
         <v>301</v>
       </c>
@@ -10403,7 +10334,7 @@
       </c>
       <c r="L204" s="4"/>
     </row>
-    <row r="205" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="4" t="n">
         <v>302</v>
       </c>
@@ -10438,7 +10369,7 @@
       </c>
       <c r="L205" s="4"/>
     </row>
-    <row r="206" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="4" t="n">
         <v>303</v>
       </c>
@@ -10473,7 +10404,7 @@
       </c>
       <c r="L206" s="4"/>
     </row>
-    <row r="207" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="4" t="n">
         <v>305</v>
       </c>
@@ -10508,7 +10439,7 @@
       </c>
       <c r="L207" s="4"/>
     </row>
-    <row r="208" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="4" t="n">
         <v>306</v>
       </c>
@@ -10543,7 +10474,7 @@
       </c>
       <c r="L208" s="4"/>
     </row>
-    <row r="209" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="4" t="n">
         <v>309</v>
       </c>
@@ -10578,7 +10509,7 @@
       </c>
       <c r="L209" s="4"/>
     </row>
-    <row r="210" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="4" t="n">
         <v>310</v>
       </c>
@@ -10613,7 +10544,7 @@
       </c>
       <c r="L210" s="4"/>
     </row>
-    <row r="211" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="4" t="n">
         <v>311</v>
       </c>
@@ -10648,7 +10579,7 @@
       </c>
       <c r="L211" s="4"/>
     </row>
-    <row r="212" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="4" t="n">
         <v>312</v>
       </c>
@@ -10757,7 +10688,7 @@
       </c>
       <c r="L214" s="4"/>
     </row>
-    <row r="215" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="4" t="n">
         <v>315</v>
       </c>
@@ -10792,7 +10723,7 @@
       </c>
       <c r="L215" s="4"/>
     </row>
-    <row r="216" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="4" t="n">
         <v>316</v>
       </c>
@@ -10827,7 +10758,7 @@
       </c>
       <c r="L216" s="4"/>
     </row>
-    <row r="217" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="4" t="n">
         <v>317</v>
       </c>
@@ -10899,7 +10830,7 @@
       </c>
       <c r="L218" s="4"/>
     </row>
-    <row r="219" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="4" t="n">
         <v>319</v>
       </c>
@@ -10934,7 +10865,7 @@
       </c>
       <c r="L219" s="4"/>
     </row>
-    <row r="220" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="4" t="n">
         <v>320</v>
       </c>
@@ -10969,7 +10900,7 @@
       </c>
       <c r="L220" s="4"/>
     </row>
-    <row r="221" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="4" t="n">
         <v>321</v>
       </c>
@@ -11004,7 +10935,7 @@
       </c>
       <c r="L221" s="4"/>
     </row>
-    <row r="222" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="4" t="n">
         <v>322</v>
       </c>
@@ -11039,7 +10970,7 @@
       </c>
       <c r="L222" s="4"/>
     </row>
-    <row r="223" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="4" t="n">
         <v>323</v>
       </c>
@@ -11074,7 +11005,7 @@
       </c>
       <c r="L223" s="4"/>
     </row>
-    <row r="224" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="4" t="n">
         <v>324</v>
       </c>
@@ -11109,7 +11040,7 @@
       </c>
       <c r="L224" s="4"/>
     </row>
-    <row r="225" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="4" t="n">
         <v>325</v>
       </c>
@@ -11144,7 +11075,7 @@
       </c>
       <c r="L225" s="4"/>
     </row>
-    <row r="226" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="4" t="n">
         <v>326</v>
       </c>
@@ -11179,7 +11110,7 @@
       </c>
       <c r="L226" s="4"/>
     </row>
-    <row r="227" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="4" t="n">
         <v>329</v>
       </c>
@@ -11214,7 +11145,7 @@
       </c>
       <c r="L227" s="4"/>
     </row>
-    <row r="228" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="4" t="n">
         <v>330</v>
       </c>
@@ -11397,7 +11328,7 @@
       </c>
       <c r="L232" s="4"/>
     </row>
-    <row r="233" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="4" t="n">
         <v>335</v>
       </c>
@@ -11432,7 +11363,7 @@
       </c>
       <c r="L233" s="4"/>
     </row>
-    <row r="234" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="4" t="n">
         <v>336</v>
       </c>
@@ -11467,7 +11398,7 @@
       </c>
       <c r="L234" s="4"/>
     </row>
-    <row r="235" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="4" t="n">
         <v>337</v>
       </c>
@@ -11537,7 +11468,7 @@
       </c>
       <c r="L236" s="4"/>
     </row>
-    <row r="237" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="4" t="n">
         <v>339</v>
       </c>
@@ -11572,7 +11503,7 @@
       </c>
       <c r="L237" s="4"/>
     </row>
-    <row r="238" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="4" t="n">
         <v>340</v>
       </c>
@@ -11681,7 +11612,7 @@
       </c>
       <c r="L240" s="4"/>
     </row>
-    <row r="241" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="4" t="n">
         <v>346</v>
       </c>
@@ -11716,7 +11647,7 @@
       </c>
       <c r="L241" s="4"/>
     </row>
-    <row r="242" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="4" t="n">
         <v>347</v>
       </c>
@@ -11751,7 +11682,7 @@
       </c>
       <c r="L242" s="4"/>
     </row>
-    <row r="243" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="4" t="n">
         <v>349</v>
       </c>
@@ -11823,7 +11754,7 @@
       </c>
       <c r="L244" s="4"/>
     </row>
-    <row r="245" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="4" t="n">
         <v>351</v>
       </c>
@@ -11858,7 +11789,7 @@
       </c>
       <c r="L245" s="4"/>
     </row>
-    <row r="246" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="4" t="n">
         <v>352</v>
       </c>
@@ -11893,7 +11824,7 @@
       </c>
       <c r="L246" s="4"/>
     </row>
-    <row r="247" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="4" t="n">
         <v>353</v>
       </c>
@@ -11928,7 +11859,7 @@
       </c>
       <c r="L247" s="4"/>
     </row>
-    <row r="248" customFormat="false" ht="14.25" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="4" t="n">
         <v>354</v>
       </c>
@@ -11963,7 +11894,7 @@
       </c>
       <c r="L248" s="4"/>
     </row>
-    <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="8" t="n">
         <v>247</v>
       </c>
@@ -11999,7 +11930,7 @@
       </c>
       <c r="L249" s="8"/>
     </row>
-    <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="8" t="n">
         <v>248</v>
       </c>
@@ -12035,7 +11966,7 @@
       </c>
       <c r="L250" s="8"/>
     </row>
-    <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="8" t="n">
         <v>249</v>
       </c>
@@ -12071,7 +12002,7 @@
       </c>
       <c r="L251" s="8"/>
     </row>
-    <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="8" t="n">
         <v>250</v>
       </c>
@@ -12107,266 +12038,8 @@
       </c>
       <c r="L252" s="8"/>
     </row>
-    <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="8" t="n">
-        <v>251</v>
-      </c>
-      <c r="B253" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C253" s="10" t="s">
-        <v>796</v>
-      </c>
-      <c r="D253" s="10" t="s">
-        <v>797</v>
-      </c>
-      <c r="E253" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F253" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="G253" s="10" t="s">
-        <v>798</v>
-      </c>
-      <c r="H253" s="8" t="s">
-        <v>799</v>
-      </c>
-      <c r="I253" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J253" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="K253" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L253" s="8"/>
-    </row>
-    <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="8" t="n">
-        <v>252</v>
-      </c>
-      <c r="B254" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C254" s="10" t="s">
-        <v>800</v>
-      </c>
-      <c r="D254" s="10" t="s">
-        <v>801</v>
-      </c>
-      <c r="E254" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F254" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="G254" s="10" t="s">
-        <v>784</v>
-      </c>
-      <c r="H254" s="8" t="s">
-        <v>802</v>
-      </c>
-      <c r="I254" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J254" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="K254" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L254" s="8"/>
-    </row>
-    <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="8" t="n">
-        <v>253</v>
-      </c>
-      <c r="B255" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C255" s="10" t="s">
-        <v>803</v>
-      </c>
-      <c r="D255" s="10" t="s">
-        <v>804</v>
-      </c>
-      <c r="E255" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F255" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G255" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="H255" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="I255" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J255" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="K255" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L255" s="8"/>
-    </row>
-    <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="8" t="n">
-        <v>254</v>
-      </c>
-      <c r="B256" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C256" s="10" t="s">
-        <v>806</v>
-      </c>
-      <c r="D256" s="10" t="s">
-        <v>807</v>
-      </c>
-      <c r="E256" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F256" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="G256" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H256" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="I256" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J256" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="K256" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L256" s="8"/>
-    </row>
-    <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="8" t="n">
-        <v>256</v>
-      </c>
-      <c r="B257" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C257" s="10" t="s">
-        <v>809</v>
-      </c>
-      <c r="D257" s="10" t="s">
-        <v>810</v>
-      </c>
-      <c r="E257" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F257" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="G257" s="10" t="s">
-        <v>784</v>
-      </c>
-      <c r="H257" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="I257" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J257" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="K257" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L257" s="8"/>
-    </row>
-    <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="8" t="n">
-        <v>257</v>
-      </c>
-      <c r="B258" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C258" s="10" t="s">
-        <v>812</v>
-      </c>
-      <c r="D258" s="10" t="s">
-        <v>813</v>
-      </c>
-      <c r="E258" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F258" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="G258" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="H258" s="8" t="s">
-        <v>814</v>
-      </c>
-      <c r="I258" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J258" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="K258" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L258" s="8"/>
-    </row>
-    <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="8" t="n">
-        <v>258</v>
-      </c>
-      <c r="B259" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C259" s="10" t="s">
-        <v>815</v>
-      </c>
-      <c r="D259" s="10" t="s">
-        <v>816</v>
-      </c>
-      <c r="E259" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F259" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="G259" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H259" s="8" t="s">
-        <v>817</v>
-      </c>
-      <c r="I259" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J259" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="K259" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L259" s="8"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:L259">
-    <filterColumn colId="9">
-      <customFilters and="true">
-        <customFilter operator="**none**" val=""/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:L248"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
@@ -12635,13 +12308,6 @@
     <hyperlink ref="B250" r:id="rId248" display="▶ Play"/>
     <hyperlink ref="B251" r:id="rId249" display="▶ Play"/>
     <hyperlink ref="B252" r:id="rId250" display="▶ Play"/>
-    <hyperlink ref="B253" r:id="rId251" display="▶ Play"/>
-    <hyperlink ref="B254" r:id="rId252" display="▶ Play"/>
-    <hyperlink ref="B255" r:id="rId253" display="▶ Play"/>
-    <hyperlink ref="B256" r:id="rId254" display="▶ Play"/>
-    <hyperlink ref="B257" r:id="rId255" display="▶ Play"/>
-    <hyperlink ref="B258" r:id="rId256" display="▶ Play"/>
-    <hyperlink ref="B259" r:id="rId257" display="▶ Play"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12650,7 +12316,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId258"/>
+  <drawing r:id="rId251"/>
 </worksheet>
 </file>
 
@@ -12669,90 +12335,90 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>819</v>
+        <v>797</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>820</v>
+        <v>798</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>821</v>
+        <v>799</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>822</v>
+        <v>800</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>823</v>
+        <v>801</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>824</v>
+        <v>802</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>825</v>
+        <v>803</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>826</v>
+        <v>804</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>827</v>
+        <v>805</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>828</v>
+        <v>806</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>829</v>
+        <v>807</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>830</v>
+        <v>808</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>831</v>
+        <v>809</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>832</v>
+        <v>810</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>833</v>
+        <v>811</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>834</v>
+        <v>812</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>835</v>
+        <v>32</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>836</v>
+        <v>813</v>
       </c>
     </row>
   </sheetData>
@@ -12782,24 +12448,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>837</v>
+        <v>814</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>838</v>
+        <v>815</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>839</v>
+        <v>816</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>841</v>
+        <v>818</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
       <c r="B2" s="6" t="n">
         <v>0</v>
@@ -12808,13 +12474,13 @@
         <v>6</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>843</v>
+        <v>820</v>
       </c>
       <c r="E2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>844</v>
+        <v>821</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>6</v>
@@ -12823,15 +12489,15 @@
         <v>10</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>845</v>
+        <v>822</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>846</v>
+        <v>823</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>10</v>
@@ -12840,7 +12506,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>791</v>
@@ -12848,7 +12514,7 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>849</v>
+        <v>826</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>14</v>
@@ -12857,15 +12523,15 @@
         <v>17</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>850</v>
+        <v>827</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>846</v>
+        <v>823</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>17</v>
@@ -12874,13 +12540,13 @@
         <v>20</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>852</v>
+        <v>829</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>853</v>
+        <v>830</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>20</v>
@@ -12889,10 +12555,10 @@
         <v>24</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>854</v>
+        <v>831</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>846</v>
+        <v>823</v>
       </c>
     </row>
   </sheetData>
@@ -12924,10 +12590,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>855</v>
+        <v>832</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>856</v>
+        <v>833</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12939,7 +12605,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12951,7 +12617,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12975,7 +12641,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12987,7 +12653,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12999,7 +12665,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13023,7 +12689,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13095,7 +12761,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13119,7 +12785,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13131,7 +12797,7 @@
         <v>13</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13155,7 +12821,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13167,7 +12833,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13179,7 +12845,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13203,7 +12869,7 @@
         <v>15</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13215,7 +12881,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13251,7 +12917,7 @@
         <v>6</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13275,7 +12941,7 @@
         <v>8</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
